--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,2159 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118081330</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78480</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483456</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6948507</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118083771</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97836</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483183</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6948595</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118081924</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78480</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483340</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6948561</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118083349</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78217</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483198</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6948758</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118082904</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79562</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6948740</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118082031</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79561</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483339</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6948654</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118081681</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78216</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483423</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6948444</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118083906</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97836</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483232</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6948534</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118081844</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74592</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483376</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6948461</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fuktigt parti med många senvuxna gamla granar</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118081515</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78216</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483474</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6948475</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118083454</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56499</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>483155</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6948741</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flög iväg skrämd. Blockig tallskog.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118082854</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79561</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483265</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6948740</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118085070</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78217</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483195</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6948648</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118084199</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90648</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483087</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6948705</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med överväxta kolade hållbara lågor av tall.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118085065</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78480</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483269</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6948638</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118085047</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79590</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483455</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6948481</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118085086</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78216</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>483191</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6948535</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118085061</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79098</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483237</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6948734</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118085059</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79589</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483427</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6948440</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118081330</v>
+        <v>118083349</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483456</v>
+        <v>483198</v>
       </c>
       <c r="R10" t="n">
-        <v>6948507</v>
+        <v>6948758</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118083771</v>
+        <v>118081515</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>78216</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,47 +1753,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483183</v>
+        <v>483474</v>
       </c>
       <c r="R11" t="n">
-        <v>6948595</v>
+        <v>6948475</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1825,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118081924</v>
+        <v>118083906</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,38 +1865,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483340</v>
+        <v>483232</v>
       </c>
       <c r="R12" t="n">
-        <v>6948561</v>
+        <v>6948534</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118083349</v>
+        <v>118082854</v>
       </c>
       <c r="B13" t="n">
-        <v>78217</v>
+        <v>79561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483198</v>
+        <v>483265</v>
       </c>
       <c r="R13" t="n">
-        <v>6948758</v>
+        <v>6948740</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118082904</v>
+        <v>118081844</v>
       </c>
       <c r="B14" t="n">
-        <v>79562</v>
+        <v>74592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483265</v>
+        <v>483376</v>
       </c>
       <c r="R14" t="n">
-        <v>6948740</v>
+        <v>6948461</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,7 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fuktigt parti med många senvuxna gamla granar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118082031</v>
+        <v>118083454</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>56499</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,41 +2215,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483339</v>
+        <v>483155</v>
       </c>
       <c r="R15" t="n">
-        <v>6948654</v>
+        <v>6948741</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flög iväg skrämd. Blockig tallskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118081681</v>
+        <v>118081330</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,21 +2355,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2350,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483423</v>
+        <v>483456</v>
       </c>
       <c r="R16" t="n">
-        <v>6948444</v>
+        <v>6948507</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2385,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2395,7 +2424,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118083906</v>
+        <v>118082031</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,47 +2463,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483232</v>
+        <v>483339</v>
       </c>
       <c r="R17" t="n">
-        <v>6948534</v>
+        <v>6948654</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2506,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2536,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,10 +2563,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118081844</v>
+        <v>118081681</v>
       </c>
       <c r="B18" t="n">
-        <v>74592</v>
+        <v>78216</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,21 +2579,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2583,10 +2603,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483376</v>
+        <v>483423</v>
       </c>
       <c r="R18" t="n">
-        <v>6948461</v>
+        <v>6948444</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2618,7 +2638,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,12 +2648,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fuktigt parti med många senvuxna gamla granar</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118081515</v>
+        <v>118081924</v>
       </c>
       <c r="B19" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,21 +2691,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2700,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483474</v>
+        <v>483340</v>
       </c>
       <c r="R19" t="n">
-        <v>6948475</v>
+        <v>6948561</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2735,7 +2750,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2760,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118083454</v>
+        <v>118082904</v>
       </c>
       <c r="B20" t="n">
-        <v>56499</v>
+        <v>79562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2784,60 +2799,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483155</v>
+        <v>483265</v>
       </c>
       <c r="R20" t="n">
-        <v>6948741</v>
+        <v>6948740</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,7 +2862,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,12 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>21:49</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flög iväg skrämd. Blockig tallskog.</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2908,10 +2899,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118082854</v>
+        <v>118083771</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2920,38 +2911,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483265</v>
+        <v>483183</v>
       </c>
       <c r="R21" t="n">
-        <v>6948740</v>
+        <v>6948595</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118085070</v>
+        <v>118085061</v>
       </c>
       <c r="B22" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,21 +3036,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483195</v>
+        <v>483237</v>
       </c>
       <c r="R22" t="n">
-        <v>6948648</v>
+        <v>6948734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118085061</v>
+        <v>118085059</v>
       </c>
       <c r="B27" t="n">
-        <v>79098</v>
+        <v>79589</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3582,25 +3582,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483237</v>
+        <v>483427</v>
       </c>
       <c r="R27" t="n">
-        <v>6948734</v>
+        <v>6948440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118085059</v>
+        <v>118085070</v>
       </c>
       <c r="B28" t="n">
-        <v>79589</v>
+        <v>78217</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3688,25 +3688,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483427</v>
+        <v>483195</v>
       </c>
       <c r="R28" t="n">
-        <v>6948440</v>
+        <v>6948648</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118083349</v>
+        <v>118082031</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483198</v>
+        <v>483339</v>
       </c>
       <c r="R10" t="n">
-        <v>6948758</v>
+        <v>6948654</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118081515</v>
+        <v>118083349</v>
       </c>
       <c r="B11" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483474</v>
+        <v>483198</v>
       </c>
       <c r="R11" t="n">
-        <v>6948475</v>
+        <v>6948758</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118083906</v>
+        <v>118081330</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,47 +1865,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483232</v>
+        <v>483456</v>
       </c>
       <c r="R12" t="n">
-        <v>6948534</v>
+        <v>6948507</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1937,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118082854</v>
+        <v>118081844</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>74594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,21 +1981,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2014,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483265</v>
+        <v>483376</v>
       </c>
       <c r="R13" t="n">
-        <v>6948740</v>
+        <v>6948461</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2049,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2050,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fuktigt parti med många senvuxna gamla granar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118081844</v>
+        <v>118081681</v>
       </c>
       <c r="B14" t="n">
-        <v>74592</v>
+        <v>78218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,21 +2098,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483376</v>
+        <v>483423</v>
       </c>
       <c r="R14" t="n">
-        <v>6948461</v>
+        <v>6948444</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2161,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fuktigt parti med många senvuxna gamla granar</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,7 +2197,7 @@
         <v>118083454</v>
       </c>
       <c r="B15" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2339,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118081330</v>
+        <v>118083906</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,38 +2342,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483456</v>
+        <v>483232</v>
       </c>
       <c r="R16" t="n">
-        <v>6948507</v>
+        <v>6948534</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118082031</v>
+        <v>118082854</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483339</v>
+        <v>483265</v>
       </c>
       <c r="R17" t="n">
-        <v>6948654</v>
+        <v>6948740</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,10 +2563,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118081681</v>
+        <v>118082904</v>
       </c>
       <c r="B18" t="n">
-        <v>78216</v>
+        <v>79564</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,21 +2579,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483423</v>
+        <v>483265</v>
       </c>
       <c r="R18" t="n">
-        <v>6948444</v>
+        <v>6948740</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118081924</v>
+        <v>118083771</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2687,38 +2687,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483340</v>
+        <v>483183</v>
       </c>
       <c r="R19" t="n">
-        <v>6948561</v>
+        <v>6948595</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2750,7 +2759,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2760,7 +2769,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,10 +2796,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118082904</v>
+        <v>118081924</v>
       </c>
       <c r="B20" t="n">
-        <v>79562</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,21 +2812,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2827,10 +2836,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483265</v>
+        <v>483340</v>
       </c>
       <c r="R20" t="n">
-        <v>6948740</v>
+        <v>6948561</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2862,7 +2871,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2872,7 +2881,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,10 +2908,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118083771</v>
+        <v>118081515</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>78218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2911,47 +2920,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483183</v>
+        <v>483474</v>
       </c>
       <c r="R21" t="n">
-        <v>6948595</v>
+        <v>6948475</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118085061</v>
+        <v>118085047</v>
       </c>
       <c r="B22" t="n">
-        <v>79098</v>
+        <v>79592</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,25 +3032,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483237</v>
+        <v>483455</v>
       </c>
       <c r="R22" t="n">
-        <v>6948734</v>
+        <v>6948481</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118084199</v>
+        <v>118085070</v>
       </c>
       <c r="B23" t="n">
-        <v>90648</v>
+        <v>78219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,25 +3138,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3165,17 +3165,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
+          <t>Mörttjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483087</v>
+        <v>483195</v>
       </c>
       <c r="R23" t="n">
-        <v>6948705</v>
+        <v>6948648</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3202,24 +3202,9 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>22:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>22:46</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med överväxta kolade hållbara lågor av tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3250,7 +3235,7 @@
         <v>118085065</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3358,10 +3343,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118085047</v>
+        <v>118084199</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>90650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,25 +3355,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3397,17 +3382,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörttjärnberget, Jmt</t>
+          <t>Mörttjärnen (Mörttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483455</v>
+        <v>483087</v>
       </c>
       <c r="R25" t="n">
-        <v>6948481</v>
+        <v>6948705</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3434,9 +3419,24 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med överväxta kolade hållbara lågor av tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118085086</v>
+        <v>118085061</v>
       </c>
       <c r="B26" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483191</v>
+        <v>483237</v>
       </c>
       <c r="R26" t="n">
-        <v>6948535</v>
+        <v>6948734</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
         <v>118085059</v>
       </c>
       <c r="B27" t="n">
-        <v>79589</v>
+        <v>79591</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118085070</v>
+        <v>118085086</v>
       </c>
       <c r="B28" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483195</v>
+        <v>483191</v>
       </c>
       <c r="R28" t="n">
-        <v>6948648</v>
+        <v>6948535</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3779,6 +3779,1346 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118123421</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483177</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6948815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118118172</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78219</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>482995</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6948649</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118118166</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78218</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>482995</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6948649</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118118273</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483018</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6948644</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118123432</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86818</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>510</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483196</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6948818</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118118347</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78218</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>482997</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6948787</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118118175</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79100</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>482995</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6948649</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118119339</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483132</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6948839</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118119090</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>483141</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6948860</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118117836</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>482942</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6948718</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118120706</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget (Mörttjärnberget), Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483180</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6948802</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118123417</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78219</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mörttjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483047</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6948839</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178695</v>
+        <v>122178673</v>
       </c>
       <c r="B41" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483360</v>
+        <v>483127</v>
       </c>
       <c r="R41" t="n">
-        <v>6948597</v>
+        <v>6948551</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178694</v>
+        <v>122178725</v>
       </c>
       <c r="B42" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483393</v>
+        <v>483174</v>
       </c>
       <c r="R42" t="n">
-        <v>6948545</v>
+        <v>6948830</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178674</v>
+        <v>122178688</v>
       </c>
       <c r="B43" t="n">
-        <v>98175</v>
+        <v>79726</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483168</v>
+        <v>483425</v>
       </c>
       <c r="R43" t="n">
-        <v>6948539</v>
+        <v>6948524</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178682</v>
+        <v>122178684</v>
       </c>
       <c r="B44" t="n">
-        <v>98196</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483452</v>
+        <v>483433</v>
       </c>
       <c r="R44" t="n">
-        <v>6948488</v>
+        <v>6948515</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178697</v>
+        <v>122178687</v>
       </c>
       <c r="B45" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483357</v>
+        <v>483437</v>
       </c>
       <c r="R45" t="n">
-        <v>6948607</v>
+        <v>6948523</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178689</v>
+        <v>122178691</v>
       </c>
       <c r="B46" t="n">
-        <v>79726</v>
+        <v>98092</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483427</v>
+        <v>483406</v>
       </c>
       <c r="R46" t="n">
-        <v>6948511</v>
+        <v>6948521</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178699</v>
+        <v>122178682</v>
       </c>
       <c r="B47" t="n">
-        <v>98175</v>
+        <v>98196</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483311</v>
+        <v>483452</v>
       </c>
       <c r="R47" t="n">
-        <v>6948661</v>
+        <v>6948488</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178701</v>
+        <v>122178679</v>
       </c>
       <c r="B48" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483306</v>
+        <v>483412</v>
       </c>
       <c r="R48" t="n">
-        <v>6948674</v>
+        <v>6948450</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178703</v>
+        <v>122178681</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>78381</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483313</v>
+        <v>483465</v>
       </c>
       <c r="R49" t="n">
-        <v>6948690</v>
+        <v>6948486</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178684</v>
+        <v>122178702</v>
       </c>
       <c r="B50" t="n">
-        <v>79726</v>
+        <v>97129</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6055,25 +6055,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483433</v>
+        <v>483308</v>
       </c>
       <c r="R50" t="n">
-        <v>6948515</v>
+        <v>6948678</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178691</v>
+        <v>122178683</v>
       </c>
       <c r="B51" t="n">
-        <v>98092</v>
+        <v>98175</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483406</v>
+        <v>483448</v>
       </c>
       <c r="R51" t="n">
-        <v>6948521</v>
+        <v>6948496</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178683</v>
+        <v>122178677</v>
       </c>
       <c r="B52" t="n">
-        <v>98175</v>
+        <v>97129</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6259,25 +6259,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483448</v>
+        <v>483297</v>
       </c>
       <c r="R52" t="n">
-        <v>6948496</v>
+        <v>6948492</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178692</v>
+        <v>122178678</v>
       </c>
       <c r="B53" t="n">
-        <v>97129</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483406</v>
+        <v>483411</v>
       </c>
       <c r="R53" t="n">
-        <v>6948521</v>
+        <v>6948445</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,7 +6451,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178679</v>
+        <v>122178695</v>
       </c>
       <c r="B54" t="n">
         <v>78645</v>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483412</v>
+        <v>483360</v>
       </c>
       <c r="R54" t="n">
-        <v>6948450</v>
+        <v>6948597</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178700</v>
+        <v>122178674</v>
       </c>
       <c r="B55" t="n">
-        <v>98196</v>
+        <v>98175</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483303</v>
+        <v>483168</v>
       </c>
       <c r="R55" t="n">
-        <v>6948673</v>
+        <v>6948539</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178681</v>
+        <v>122178699</v>
       </c>
       <c r="B56" t="n">
-        <v>78381</v>
+        <v>98175</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6667,25 +6667,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483465</v>
+        <v>483311</v>
       </c>
       <c r="R56" t="n">
-        <v>6948486</v>
+        <v>6948661</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178687</v>
+        <v>122178675</v>
       </c>
       <c r="B57" t="n">
-        <v>79726</v>
+        <v>98175</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483437</v>
+        <v>483206</v>
       </c>
       <c r="R57" t="n">
-        <v>6948523</v>
+        <v>6948535</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178726</v>
+        <v>122178671</v>
       </c>
       <c r="B58" t="n">
         <v>78382</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483017</v>
+        <v>483025</v>
       </c>
       <c r="R58" t="n">
-        <v>6948711</v>
+        <v>6948533</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178702</v>
+        <v>122178676</v>
       </c>
       <c r="B59" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6973,25 +6973,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483308</v>
+        <v>483258</v>
       </c>
       <c r="R59" t="n">
-        <v>6948678</v>
+        <v>6948497</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178693</v>
+        <v>122178701</v>
       </c>
       <c r="B60" t="n">
-        <v>98196</v>
+        <v>79726</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483400</v>
+        <v>483306</v>
       </c>
       <c r="R60" t="n">
-        <v>6948533</v>
+        <v>6948674</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178676</v>
+        <v>122178698</v>
       </c>
       <c r="B61" t="n">
-        <v>78645</v>
+        <v>98175</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483258</v>
+        <v>483316</v>
       </c>
       <c r="R61" t="n">
-        <v>6948497</v>
+        <v>6948659</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178685</v>
+        <v>122178669</v>
       </c>
       <c r="B62" t="n">
-        <v>79726</v>
+        <v>98196</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483448</v>
+        <v>482972</v>
       </c>
       <c r="R62" t="n">
-        <v>6948530</v>
+        <v>6948524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178677</v>
+        <v>122178727</v>
       </c>
       <c r="B63" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483297</v>
+        <v>482951</v>
       </c>
       <c r="R63" t="n">
-        <v>6948492</v>
+        <v>6948660</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178725</v>
+        <v>122178694</v>
       </c>
       <c r="B64" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7483,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483174</v>
+        <v>483393</v>
       </c>
       <c r="R64" t="n">
-        <v>6948830</v>
+        <v>6948545</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178678</v>
+        <v>122178700</v>
       </c>
       <c r="B65" t="n">
-        <v>98079</v>
+        <v>98196</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483411</v>
+        <v>483303</v>
       </c>
       <c r="R65" t="n">
-        <v>6948445</v>
+        <v>6948673</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178698</v>
+        <v>122178672</v>
       </c>
       <c r="B66" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483316</v>
+        <v>483111</v>
       </c>
       <c r="R66" t="n">
-        <v>6948659</v>
+        <v>6948568</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178673</v>
+        <v>122178703</v>
       </c>
       <c r="B67" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7789,25 +7789,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483127</v>
+        <v>483313</v>
       </c>
       <c r="R67" t="n">
-        <v>6948551</v>
+        <v>6948690</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178671</v>
+        <v>122178692</v>
       </c>
       <c r="B68" t="n">
-        <v>78382</v>
+        <v>97129</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7891,25 +7891,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483025</v>
+        <v>483406</v>
       </c>
       <c r="R68" t="n">
-        <v>6948533</v>
+        <v>6948521</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178669</v>
+        <v>122178726</v>
       </c>
       <c r="B69" t="n">
-        <v>98196</v>
+        <v>78382</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482972</v>
+        <v>483017</v>
       </c>
       <c r="R69" t="n">
-        <v>6948524</v>
+        <v>6948711</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178675</v>
+        <v>122178680</v>
       </c>
       <c r="B71" t="n">
-        <v>98175</v>
+        <v>79630</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483206</v>
+        <v>483471</v>
       </c>
       <c r="R71" t="n">
-        <v>6948535</v>
+        <v>6948473</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178688</v>
+        <v>122178689</v>
       </c>
       <c r="B72" t="n">
         <v>79726</v>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483425</v>
+        <v>483427</v>
       </c>
       <c r="R72" t="n">
-        <v>6948524</v>
+        <v>6948511</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178672</v>
+        <v>122178697</v>
       </c>
       <c r="B73" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483111</v>
+        <v>483357</v>
       </c>
       <c r="R73" t="n">
-        <v>6948568</v>
+        <v>6948607</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178727</v>
+        <v>122178693</v>
       </c>
       <c r="B74" t="n">
-        <v>78645</v>
+        <v>98196</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482951</v>
+        <v>483400</v>
       </c>
       <c r="R74" t="n">
-        <v>6948660</v>
+        <v>6948533</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178680</v>
+        <v>122178685</v>
       </c>
       <c r="B75" t="n">
-        <v>79630</v>
+        <v>79726</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483471</v>
+        <v>483448</v>
       </c>
       <c r="R75" t="n">
-        <v>6948473</v>
+        <v>6948530</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178684</v>
+        <v>122178682</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>98196</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483433</v>
+        <v>483452</v>
       </c>
       <c r="R44" t="n">
-        <v>6948515</v>
+        <v>6948488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178687</v>
+        <v>122178684</v>
       </c>
       <c r="B45" t="n">
         <v>79726</v>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483437</v>
+        <v>483433</v>
       </c>
       <c r="R45" t="n">
-        <v>6948523</v>
+        <v>6948515</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178691</v>
+        <v>122178687</v>
       </c>
       <c r="B46" t="n">
-        <v>98092</v>
+        <v>79726</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483406</v>
+        <v>483437</v>
       </c>
       <c r="R46" t="n">
-        <v>6948521</v>
+        <v>6948523</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178682</v>
+        <v>122178679</v>
       </c>
       <c r="B47" t="n">
-        <v>98196</v>
+        <v>78645</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483452</v>
+        <v>483412</v>
       </c>
       <c r="R47" t="n">
-        <v>6948488</v>
+        <v>6948450</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178679</v>
+        <v>122178691</v>
       </c>
       <c r="B48" t="n">
-        <v>78645</v>
+        <v>98092</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483412</v>
+        <v>483406</v>
       </c>
       <c r="R48" t="n">
-        <v>6948450</v>
+        <v>6948521</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178680</v>
+        <v>122178689</v>
       </c>
       <c r="B71" t="n">
-        <v>79630</v>
+        <v>79726</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483471</v>
+        <v>483427</v>
       </c>
       <c r="R71" t="n">
-        <v>6948473</v>
+        <v>6948511</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178689</v>
+        <v>122178680</v>
       </c>
       <c r="B72" t="n">
-        <v>79726</v>
+        <v>79630</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8299,25 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483427</v>
+        <v>483471</v>
       </c>
       <c r="R72" t="n">
-        <v>6948511</v>
+        <v>6948473</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178693</v>
+        <v>122178685</v>
       </c>
       <c r="B74" t="n">
-        <v>98196</v>
+        <v>79726</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483400</v>
+        <v>483448</v>
       </c>
       <c r="R74" t="n">
-        <v>6948533</v>
+        <v>6948530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178685</v>
+        <v>122178693</v>
       </c>
       <c r="B75" t="n">
-        <v>79726</v>
+        <v>98196</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483448</v>
+        <v>483400</v>
       </c>
       <c r="R75" t="n">
-        <v>6948530</v>
+        <v>6948533</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5128,7 +5128,7 @@
         <v>122178673</v>
       </c>
       <c r="B41" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178725</v>
+        <v>122178698</v>
       </c>
       <c r="B42" t="n">
-        <v>97129</v>
+        <v>98185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483174</v>
+        <v>483316</v>
       </c>
       <c r="R42" t="n">
-        <v>6948830</v>
+        <v>6948659</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178688</v>
+        <v>122178687</v>
       </c>
       <c r="B43" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483425</v>
+        <v>483437</v>
       </c>
       <c r="R43" t="n">
-        <v>6948524</v>
+        <v>6948523</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178682</v>
+        <v>122178697</v>
       </c>
       <c r="B44" t="n">
-        <v>98196</v>
+        <v>97139</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5447,21 +5447,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483452</v>
+        <v>483357</v>
       </c>
       <c r="R44" t="n">
-        <v>6948488</v>
+        <v>6948607</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178684</v>
+        <v>122178680</v>
       </c>
       <c r="B45" t="n">
-        <v>79726</v>
+        <v>79631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483433</v>
+        <v>483471</v>
       </c>
       <c r="R45" t="n">
-        <v>6948515</v>
+        <v>6948473</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178687</v>
+        <v>122178694</v>
       </c>
       <c r="B46" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483437</v>
+        <v>483393</v>
       </c>
       <c r="R46" t="n">
-        <v>6948523</v>
+        <v>6948545</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5740,7 +5740,7 @@
         <v>122178679</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178691</v>
+        <v>122178678</v>
       </c>
       <c r="B48" t="n">
-        <v>98092</v>
+        <v>98089</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483406</v>
+        <v>483411</v>
       </c>
       <c r="R48" t="n">
-        <v>6948521</v>
+        <v>6948445</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178681</v>
+        <v>122178675</v>
       </c>
       <c r="B49" t="n">
-        <v>78381</v>
+        <v>98185</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483465</v>
+        <v>483206</v>
       </c>
       <c r="R49" t="n">
-        <v>6948486</v>
+        <v>6948535</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178702</v>
+        <v>122178685</v>
       </c>
       <c r="B50" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6055,25 +6055,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483308</v>
+        <v>483448</v>
       </c>
       <c r="R50" t="n">
-        <v>6948678</v>
+        <v>6948530</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178683</v>
+        <v>122178692</v>
       </c>
       <c r="B51" t="n">
-        <v>98175</v>
+        <v>97139</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483448</v>
+        <v>483406</v>
       </c>
       <c r="R51" t="n">
-        <v>6948496</v>
+        <v>6948521</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178677</v>
+        <v>122178725</v>
       </c>
       <c r="B52" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483297</v>
+        <v>483174</v>
       </c>
       <c r="R52" t="n">
-        <v>6948492</v>
+        <v>6948830</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178678</v>
+        <v>122178727</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>78646</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,25 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483411</v>
+        <v>482951</v>
       </c>
       <c r="R53" t="n">
-        <v>6948445</v>
+        <v>6948660</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178695</v>
+        <v>122178672</v>
       </c>
       <c r="B54" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483360</v>
+        <v>483111</v>
       </c>
       <c r="R54" t="n">
-        <v>6948597</v>
+        <v>6948568</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178674</v>
+        <v>122178702</v>
       </c>
       <c r="B55" t="n">
-        <v>98175</v>
+        <v>97139</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483168</v>
+        <v>483308</v>
       </c>
       <c r="R55" t="n">
-        <v>6948539</v>
+        <v>6948678</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178699</v>
+        <v>122178669</v>
       </c>
       <c r="B56" t="n">
-        <v>98175</v>
+        <v>98206</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6667,25 +6667,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483311</v>
+        <v>482972</v>
       </c>
       <c r="R56" t="n">
-        <v>6948661</v>
+        <v>6948524</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178675</v>
+        <v>122178695</v>
       </c>
       <c r="B57" t="n">
-        <v>98175</v>
+        <v>78646</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483206</v>
+        <v>483360</v>
       </c>
       <c r="R57" t="n">
-        <v>6948535</v>
+        <v>6948597</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178671</v>
+        <v>122178674</v>
       </c>
       <c r="B58" t="n">
-        <v>78382</v>
+        <v>98185</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483025</v>
+        <v>483168</v>
       </c>
       <c r="R58" t="n">
-        <v>6948533</v>
+        <v>6948539</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178676</v>
+        <v>122178689</v>
       </c>
       <c r="B59" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483258</v>
+        <v>483427</v>
       </c>
       <c r="R59" t="n">
-        <v>6948497</v>
+        <v>6948511</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178701</v>
+        <v>122178683</v>
       </c>
       <c r="B60" t="n">
-        <v>79726</v>
+        <v>98185</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483306</v>
+        <v>483448</v>
       </c>
       <c r="R60" t="n">
-        <v>6948674</v>
+        <v>6948496</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178698</v>
+        <v>122178682</v>
       </c>
       <c r="B61" t="n">
-        <v>98175</v>
+        <v>98206</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483316</v>
+        <v>483452</v>
       </c>
       <c r="R61" t="n">
-        <v>6948659</v>
+        <v>6948488</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178669</v>
+        <v>122178693</v>
       </c>
       <c r="B62" t="n">
-        <v>98196</v>
+        <v>98206</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>482972</v>
+        <v>483400</v>
       </c>
       <c r="R62" t="n">
-        <v>6948524</v>
+        <v>6948533</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178727</v>
+        <v>122178676</v>
       </c>
       <c r="B63" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>482951</v>
+        <v>483258</v>
       </c>
       <c r="R63" t="n">
-        <v>6948660</v>
+        <v>6948497</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178694</v>
+        <v>122178681</v>
       </c>
       <c r="B64" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7487,21 +7487,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483393</v>
+        <v>483465</v>
       </c>
       <c r="R64" t="n">
-        <v>6948545</v>
+        <v>6948486</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178700</v>
+        <v>122178684</v>
       </c>
       <c r="B65" t="n">
-        <v>98196</v>
+        <v>79727</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7585,25 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483303</v>
+        <v>483433</v>
       </c>
       <c r="R65" t="n">
-        <v>6948673</v>
+        <v>6948515</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178672</v>
+        <v>122178671</v>
       </c>
       <c r="B66" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483111</v>
+        <v>483025</v>
       </c>
       <c r="R66" t="n">
-        <v>6948568</v>
+        <v>6948533</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178703</v>
+        <v>122178700</v>
       </c>
       <c r="B67" t="n">
-        <v>79726</v>
+        <v>98206</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7789,25 +7789,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483313</v>
+        <v>483303</v>
       </c>
       <c r="R67" t="n">
-        <v>6948690</v>
+        <v>6948673</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178692</v>
+        <v>122178686</v>
       </c>
       <c r="B68" t="n">
-        <v>97129</v>
+        <v>98206</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7895,21 +7895,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483406</v>
+        <v>483445</v>
       </c>
       <c r="R68" t="n">
         <v>6948521</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178726</v>
+        <v>122178691</v>
       </c>
       <c r="B69" t="n">
-        <v>78382</v>
+        <v>98102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483017</v>
+        <v>483406</v>
       </c>
       <c r="R69" t="n">
-        <v>6948711</v>
+        <v>6948521</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178686</v>
+        <v>122178701</v>
       </c>
       <c r="B70" t="n">
-        <v>98196</v>
+        <v>79727</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483445</v>
+        <v>483306</v>
       </c>
       <c r="R70" t="n">
-        <v>6948521</v>
+        <v>6948674</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178689</v>
+        <v>122178726</v>
       </c>
       <c r="B71" t="n">
-        <v>79726</v>
+        <v>78383</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8201,21 +8201,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483427</v>
+        <v>483017</v>
       </c>
       <c r="R71" t="n">
-        <v>6948511</v>
+        <v>6948711</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178680</v>
+        <v>122178677</v>
       </c>
       <c r="B72" t="n">
-        <v>79630</v>
+        <v>97139</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8303,21 +8303,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483471</v>
+        <v>483297</v>
       </c>
       <c r="R72" t="n">
-        <v>6948473</v>
+        <v>6948492</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178697</v>
+        <v>122178703</v>
       </c>
       <c r="B73" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483357</v>
+        <v>483313</v>
       </c>
       <c r="R73" t="n">
-        <v>6948607</v>
+        <v>6948690</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178685</v>
+        <v>122178688</v>
       </c>
       <c r="B74" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483448</v>
+        <v>483425</v>
       </c>
       <c r="R74" t="n">
-        <v>6948530</v>
+        <v>6948524</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178693</v>
+        <v>122178699</v>
       </c>
       <c r="B75" t="n">
-        <v>98196</v>
+        <v>98185</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483400</v>
+        <v>483311</v>
       </c>
       <c r="R75" t="n">
-        <v>6948533</v>
+        <v>6948661</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178673</v>
+        <v>122178687</v>
       </c>
       <c r="B41" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483127</v>
+        <v>483437</v>
       </c>
       <c r="R41" t="n">
-        <v>6948551</v>
+        <v>6948523</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178698</v>
+        <v>122178699</v>
       </c>
       <c r="B42" t="n">
         <v>98185</v>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483316</v>
+        <v>483311</v>
       </c>
       <c r="R42" t="n">
-        <v>6948659</v>
+        <v>6948661</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178687</v>
+        <v>122178683</v>
       </c>
       <c r="B43" t="n">
-        <v>79727</v>
+        <v>98185</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483437</v>
+        <v>483448</v>
       </c>
       <c r="R43" t="n">
-        <v>6948523</v>
+        <v>6948496</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178697</v>
+        <v>122178679</v>
       </c>
       <c r="B44" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483357</v>
+        <v>483412</v>
       </c>
       <c r="R44" t="n">
-        <v>6948607</v>
+        <v>6948450</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178680</v>
+        <v>122178689</v>
       </c>
       <c r="B45" t="n">
-        <v>79631</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483471</v>
+        <v>483427</v>
       </c>
       <c r="R45" t="n">
-        <v>6948473</v>
+        <v>6948511</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178694</v>
+        <v>122178700</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483393</v>
+        <v>483303</v>
       </c>
       <c r="R46" t="n">
-        <v>6948545</v>
+        <v>6948673</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178679</v>
+        <v>122178686</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483412</v>
+        <v>483445</v>
       </c>
       <c r="R47" t="n">
-        <v>6948450</v>
+        <v>6948521</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178678</v>
+        <v>122178698</v>
       </c>
       <c r="B48" t="n">
-        <v>98089</v>
+        <v>98185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483411</v>
+        <v>483316</v>
       </c>
       <c r="R48" t="n">
-        <v>6948445</v>
+        <v>6948659</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178675</v>
+        <v>122178684</v>
       </c>
       <c r="B49" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483206</v>
+        <v>483433</v>
       </c>
       <c r="R49" t="n">
-        <v>6948535</v>
+        <v>6948515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178685</v>
+        <v>122178688</v>
       </c>
       <c r="B50" t="n">
         <v>79727</v>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483448</v>
+        <v>483425</v>
       </c>
       <c r="R50" t="n">
-        <v>6948530</v>
+        <v>6948524</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178692</v>
+        <v>122178681</v>
       </c>
       <c r="B51" t="n">
-        <v>97139</v>
+        <v>78382</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483406</v>
+        <v>483465</v>
       </c>
       <c r="R51" t="n">
-        <v>6948521</v>
+        <v>6948486</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178725</v>
+        <v>122178727</v>
       </c>
       <c r="B52" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6259,25 +6259,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483174</v>
+        <v>482951</v>
       </c>
       <c r="R52" t="n">
-        <v>6948830</v>
+        <v>6948660</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178727</v>
+        <v>122178672</v>
       </c>
       <c r="B53" t="n">
         <v>78646</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>482951</v>
+        <v>483111</v>
       </c>
       <c r="R53" t="n">
-        <v>6948660</v>
+        <v>6948568</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178672</v>
+        <v>122178697</v>
       </c>
       <c r="B54" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483111</v>
+        <v>483357</v>
       </c>
       <c r="R54" t="n">
-        <v>6948568</v>
+        <v>6948607</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178702</v>
+        <v>122178673</v>
       </c>
       <c r="B55" t="n">
         <v>97139</v>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483308</v>
+        <v>483127</v>
       </c>
       <c r="R55" t="n">
-        <v>6948678</v>
+        <v>6948551</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178669</v>
+        <v>122178677</v>
       </c>
       <c r="B56" t="n">
-        <v>98206</v>
+        <v>97139</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>482972</v>
+        <v>483297</v>
       </c>
       <c r="R56" t="n">
-        <v>6948524</v>
+        <v>6948492</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178695</v>
+        <v>122178726</v>
       </c>
       <c r="B57" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6773,21 +6773,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483360</v>
+        <v>483017</v>
       </c>
       <c r="R57" t="n">
-        <v>6948597</v>
+        <v>6948711</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178674</v>
+        <v>122178671</v>
       </c>
       <c r="B58" t="n">
-        <v>98185</v>
+        <v>78383</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483168</v>
+        <v>483025</v>
       </c>
       <c r="R58" t="n">
-        <v>6948539</v>
+        <v>6948533</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178689</v>
+        <v>122178680</v>
       </c>
       <c r="B59" t="n">
-        <v>79727</v>
+        <v>79631</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6973,25 +6973,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483427</v>
+        <v>483471</v>
       </c>
       <c r="R59" t="n">
-        <v>6948511</v>
+        <v>6948473</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178683</v>
+        <v>122178702</v>
       </c>
       <c r="B60" t="n">
-        <v>98185</v>
+        <v>97139</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483448</v>
+        <v>483308</v>
       </c>
       <c r="R60" t="n">
-        <v>6948496</v>
+        <v>6948678</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178682</v>
+        <v>122178674</v>
       </c>
       <c r="B61" t="n">
-        <v>98206</v>
+        <v>98185</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483452</v>
+        <v>483168</v>
       </c>
       <c r="R61" t="n">
-        <v>6948488</v>
+        <v>6948539</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178693</v>
+        <v>122178676</v>
       </c>
       <c r="B62" t="n">
-        <v>98206</v>
+        <v>78646</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483400</v>
+        <v>483258</v>
       </c>
       <c r="R62" t="n">
-        <v>6948533</v>
+        <v>6948497</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178676</v>
+        <v>122178678</v>
       </c>
       <c r="B63" t="n">
-        <v>78646</v>
+        <v>98089</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483258</v>
+        <v>483411</v>
       </c>
       <c r="R63" t="n">
-        <v>6948497</v>
+        <v>6948445</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178681</v>
+        <v>122178701</v>
       </c>
       <c r="B64" t="n">
-        <v>78382</v>
+        <v>79727</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7487,21 +7487,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483465</v>
+        <v>483306</v>
       </c>
       <c r="R64" t="n">
-        <v>6948486</v>
+        <v>6948674</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178684</v>
+        <v>122178692</v>
       </c>
       <c r="B65" t="n">
-        <v>79727</v>
+        <v>97139</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7585,25 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483433</v>
+        <v>483406</v>
       </c>
       <c r="R65" t="n">
-        <v>6948515</v>
+        <v>6948521</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178671</v>
+        <v>122178675</v>
       </c>
       <c r="B66" t="n">
-        <v>78383</v>
+        <v>98185</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483025</v>
+        <v>483206</v>
       </c>
       <c r="R66" t="n">
-        <v>6948533</v>
+        <v>6948535</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178700</v>
+        <v>122178694</v>
       </c>
       <c r="B67" t="n">
-        <v>98206</v>
+        <v>78646</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7789,25 +7789,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483303</v>
+        <v>483393</v>
       </c>
       <c r="R67" t="n">
-        <v>6948673</v>
+        <v>6948545</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178686</v>
+        <v>122178693</v>
       </c>
       <c r="B68" t="n">
         <v>98206</v>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483445</v>
+        <v>483400</v>
       </c>
       <c r="R68" t="n">
-        <v>6948521</v>
+        <v>6948533</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178691</v>
+        <v>122178669</v>
       </c>
       <c r="B69" t="n">
-        <v>98102</v>
+        <v>98206</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483406</v>
+        <v>482972</v>
       </c>
       <c r="R69" t="n">
-        <v>6948521</v>
+        <v>6948524</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178701</v>
+        <v>122178691</v>
       </c>
       <c r="B70" t="n">
-        <v>79727</v>
+        <v>98102</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483306</v>
+        <v>483406</v>
       </c>
       <c r="R70" t="n">
-        <v>6948674</v>
+        <v>6948521</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178726</v>
+        <v>122178725</v>
       </c>
       <c r="B71" t="n">
-        <v>78383</v>
+        <v>97139</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483017</v>
+        <v>483174</v>
       </c>
       <c r="R71" t="n">
-        <v>6948711</v>
+        <v>6948830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178677</v>
+        <v>122178695</v>
       </c>
       <c r="B72" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8299,25 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483297</v>
+        <v>483360</v>
       </c>
       <c r="R72" t="n">
-        <v>6948492</v>
+        <v>6948597</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178703</v>
+        <v>122178685</v>
       </c>
       <c r="B73" t="n">
         <v>79727</v>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483313</v>
+        <v>483448</v>
       </c>
       <c r="R73" t="n">
-        <v>6948690</v>
+        <v>6948530</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178688</v>
+        <v>122178682</v>
       </c>
       <c r="B74" t="n">
-        <v>79727</v>
+        <v>98206</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483425</v>
+        <v>483452</v>
       </c>
       <c r="R74" t="n">
-        <v>6948524</v>
+        <v>6948488</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178699</v>
+        <v>122178703</v>
       </c>
       <c r="B75" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483311</v>
+        <v>483313</v>
       </c>
       <c r="R75" t="n">
-        <v>6948661</v>
+        <v>6948690</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178687</v>
+        <v>122178699</v>
       </c>
       <c r="B41" t="n">
-        <v>79727</v>
+        <v>98185</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483437</v>
+        <v>483311</v>
       </c>
       <c r="R41" t="n">
-        <v>6948523</v>
+        <v>6948661</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178699</v>
+        <v>122178687</v>
       </c>
       <c r="B42" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483311</v>
+        <v>483437</v>
       </c>
       <c r="R42" t="n">
-        <v>6948661</v>
+        <v>6948523</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178683</v>
+        <v>122178679</v>
       </c>
       <c r="B43" t="n">
-        <v>98185</v>
+        <v>78646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483448</v>
+        <v>483412</v>
       </c>
       <c r="R43" t="n">
-        <v>6948496</v>
+        <v>6948450</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178679</v>
+        <v>122178683</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>98185</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483412</v>
+        <v>483448</v>
       </c>
       <c r="R44" t="n">
-        <v>6948450</v>
+        <v>6948496</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178698</v>
+        <v>122178684</v>
       </c>
       <c r="B48" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483316</v>
+        <v>483433</v>
       </c>
       <c r="R48" t="n">
-        <v>6948659</v>
+        <v>6948515</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178684</v>
+        <v>122178688</v>
       </c>
       <c r="B49" t="n">
         <v>79727</v>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483433</v>
+        <v>483425</v>
       </c>
       <c r="R49" t="n">
-        <v>6948515</v>
+        <v>6948524</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178688</v>
+        <v>122178681</v>
       </c>
       <c r="B50" t="n">
-        <v>79727</v>
+        <v>78382</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483425</v>
+        <v>483465</v>
       </c>
       <c r="R50" t="n">
-        <v>6948524</v>
+        <v>6948486</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178681</v>
+        <v>122178698</v>
       </c>
       <c r="B51" t="n">
-        <v>78382</v>
+        <v>98185</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483465</v>
+        <v>483316</v>
       </c>
       <c r="R51" t="n">
-        <v>6948486</v>
+        <v>6948659</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178669</v>
+        <v>122178691</v>
       </c>
       <c r="B69" t="n">
-        <v>98206</v>
+        <v>98102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482972</v>
+        <v>483406</v>
       </c>
       <c r="R69" t="n">
-        <v>6948524</v>
+        <v>6948521</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178691</v>
+        <v>122178669</v>
       </c>
       <c r="B70" t="n">
-        <v>98102</v>
+        <v>98206</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8099,21 +8099,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483406</v>
+        <v>482972</v>
       </c>
       <c r="R70" t="n">
-        <v>6948521</v>
+        <v>6948524</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178725</v>
+        <v>122178695</v>
       </c>
       <c r="B71" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483174</v>
+        <v>483360</v>
       </c>
       <c r="R71" t="n">
-        <v>6948830</v>
+        <v>6948597</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178695</v>
+        <v>122178725</v>
       </c>
       <c r="B72" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8299,25 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483360</v>
+        <v>483174</v>
       </c>
       <c r="R72" t="n">
-        <v>6948597</v>
+        <v>6948830</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178685</v>
+        <v>122178682</v>
       </c>
       <c r="B73" t="n">
-        <v>79727</v>
+        <v>98206</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483448</v>
+        <v>483452</v>
       </c>
       <c r="R73" t="n">
-        <v>6948530</v>
+        <v>6948488</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178682</v>
+        <v>122178685</v>
       </c>
       <c r="B74" t="n">
-        <v>98206</v>
+        <v>79727</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483452</v>
+        <v>483448</v>
       </c>
       <c r="R74" t="n">
-        <v>6948488</v>
+        <v>6948530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178699</v>
+        <v>122178703</v>
       </c>
       <c r="B41" t="n">
-        <v>98185</v>
+        <v>79732</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483311</v>
+        <v>483313</v>
       </c>
       <c r="R41" t="n">
-        <v>6948661</v>
+        <v>6948690</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178687</v>
+        <v>122178726</v>
       </c>
       <c r="B42" t="n">
-        <v>79727</v>
+        <v>78388</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483437</v>
+        <v>483017</v>
       </c>
       <c r="R42" t="n">
-        <v>6948523</v>
+        <v>6948711</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178679</v>
+        <v>122178685</v>
       </c>
       <c r="B43" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483412</v>
+        <v>483448</v>
       </c>
       <c r="R43" t="n">
-        <v>6948450</v>
+        <v>6948530</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178683</v>
+        <v>122178686</v>
       </c>
       <c r="B44" t="n">
-        <v>98185</v>
+        <v>98218</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483448</v>
+        <v>483445</v>
       </c>
       <c r="R44" t="n">
-        <v>6948496</v>
+        <v>6948521</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178689</v>
+        <v>122178673</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483427</v>
+        <v>483127</v>
       </c>
       <c r="R45" t="n">
-        <v>6948511</v>
+        <v>6948551</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178700</v>
+        <v>122178679</v>
       </c>
       <c r="B46" t="n">
-        <v>98206</v>
+        <v>78651</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483303</v>
+        <v>483412</v>
       </c>
       <c r="R46" t="n">
-        <v>6948673</v>
+        <v>6948450</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178686</v>
+        <v>122178699</v>
       </c>
       <c r="B47" t="n">
-        <v>98206</v>
+        <v>98197</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483445</v>
+        <v>483311</v>
       </c>
       <c r="R47" t="n">
-        <v>6948521</v>
+        <v>6948661</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178684</v>
+        <v>122178692</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483433</v>
+        <v>483406</v>
       </c>
       <c r="R48" t="n">
-        <v>6948515</v>
+        <v>6948521</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178688</v>
+        <v>122178682</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>98218</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483425</v>
+        <v>483452</v>
       </c>
       <c r="R49" t="n">
-        <v>6948524</v>
+        <v>6948488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178681</v>
+        <v>122178694</v>
       </c>
       <c r="B50" t="n">
-        <v>78382</v>
+        <v>78651</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6059,21 +6059,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483465</v>
+        <v>483393</v>
       </c>
       <c r="R50" t="n">
-        <v>6948486</v>
+        <v>6948545</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178698</v>
+        <v>122178689</v>
       </c>
       <c r="B51" t="n">
-        <v>98185</v>
+        <v>79732</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483316</v>
+        <v>483427</v>
       </c>
       <c r="R51" t="n">
-        <v>6948659</v>
+        <v>6948511</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178727</v>
+        <v>122178681</v>
       </c>
       <c r="B52" t="n">
-        <v>78646</v>
+        <v>78387</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6263,21 +6263,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>482951</v>
+        <v>483465</v>
       </c>
       <c r="R52" t="n">
-        <v>6948660</v>
+        <v>6948486</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178672</v>
+        <v>122178678</v>
       </c>
       <c r="B53" t="n">
-        <v>78646</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,25 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483111</v>
+        <v>483411</v>
       </c>
       <c r="R53" t="n">
-        <v>6948568</v>
+        <v>6948445</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178697</v>
+        <v>122178676</v>
       </c>
       <c r="B54" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483357</v>
+        <v>483258</v>
       </c>
       <c r="R54" t="n">
-        <v>6948607</v>
+        <v>6948497</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178673</v>
+        <v>122178701</v>
       </c>
       <c r="B55" t="n">
-        <v>97139</v>
+        <v>79732</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483127</v>
+        <v>483306</v>
       </c>
       <c r="R55" t="n">
-        <v>6948551</v>
+        <v>6948674</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6658,7 +6658,7 @@
         <v>122178677</v>
       </c>
       <c r="B56" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178726</v>
+        <v>122178702</v>
       </c>
       <c r="B57" t="n">
-        <v>78383</v>
+        <v>97151</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483017</v>
+        <v>483308</v>
       </c>
       <c r="R57" t="n">
-        <v>6948711</v>
+        <v>6948678</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178671</v>
+        <v>122178669</v>
       </c>
       <c r="B58" t="n">
-        <v>78383</v>
+        <v>98218</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483025</v>
+        <v>482972</v>
       </c>
       <c r="R58" t="n">
-        <v>6948533</v>
+        <v>6948524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178680</v>
+        <v>122178671</v>
       </c>
       <c r="B59" t="n">
-        <v>79631</v>
+        <v>78388</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6973,25 +6973,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483471</v>
+        <v>483025</v>
       </c>
       <c r="R59" t="n">
-        <v>6948473</v>
+        <v>6948533</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178702</v>
+        <v>122178695</v>
       </c>
       <c r="B60" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483308</v>
+        <v>483360</v>
       </c>
       <c r="R60" t="n">
-        <v>6948678</v>
+        <v>6948597</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7168,7 +7168,7 @@
         <v>122178674</v>
       </c>
       <c r="B61" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178676</v>
+        <v>122178700</v>
       </c>
       <c r="B62" t="n">
-        <v>78646</v>
+        <v>98218</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483258</v>
+        <v>483303</v>
       </c>
       <c r="R62" t="n">
-        <v>6948497</v>
+        <v>6948673</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178678</v>
+        <v>122178693</v>
       </c>
       <c r="B63" t="n">
-        <v>98089</v>
+        <v>98218</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7385,21 +7385,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483411</v>
+        <v>483400</v>
       </c>
       <c r="R63" t="n">
-        <v>6948445</v>
+        <v>6948533</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178701</v>
+        <v>122178698</v>
       </c>
       <c r="B64" t="n">
-        <v>79727</v>
+        <v>98197</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7483,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483306</v>
+        <v>483316</v>
       </c>
       <c r="R64" t="n">
-        <v>6948674</v>
+        <v>6948659</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178692</v>
+        <v>122178727</v>
       </c>
       <c r="B65" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7585,25 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483406</v>
+        <v>482951</v>
       </c>
       <c r="R65" t="n">
-        <v>6948521</v>
+        <v>6948660</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178675</v>
+        <v>122178687</v>
       </c>
       <c r="B66" t="n">
-        <v>98185</v>
+        <v>79732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483206</v>
+        <v>483437</v>
       </c>
       <c r="R66" t="n">
-        <v>6948535</v>
+        <v>6948523</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178694</v>
+        <v>122178691</v>
       </c>
       <c r="B67" t="n">
-        <v>78646</v>
+        <v>98114</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7789,25 +7789,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483393</v>
+        <v>483406</v>
       </c>
       <c r="R67" t="n">
-        <v>6948545</v>
+        <v>6948521</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178693</v>
+        <v>122178680</v>
       </c>
       <c r="B68" t="n">
-        <v>98206</v>
+        <v>79636</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7895,21 +7895,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483400</v>
+        <v>483471</v>
       </c>
       <c r="R68" t="n">
-        <v>6948533</v>
+        <v>6948473</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178691</v>
+        <v>122178683</v>
       </c>
       <c r="B69" t="n">
-        <v>98102</v>
+        <v>98197</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483406</v>
+        <v>483448</v>
       </c>
       <c r="R69" t="n">
-        <v>6948521</v>
+        <v>6948496</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178669</v>
+        <v>122178684</v>
       </c>
       <c r="B70" t="n">
-        <v>98206</v>
+        <v>79732</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>482972</v>
+        <v>483433</v>
       </c>
       <c r="R70" t="n">
-        <v>6948524</v>
+        <v>6948515</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178695</v>
+        <v>122178672</v>
       </c>
       <c r="B71" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483360</v>
+        <v>483111</v>
       </c>
       <c r="R71" t="n">
-        <v>6948597</v>
+        <v>6948568</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178725</v>
+        <v>122178697</v>
       </c>
       <c r="B72" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483174</v>
+        <v>483357</v>
       </c>
       <c r="R72" t="n">
-        <v>6948830</v>
+        <v>6948607</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178682</v>
+        <v>122178675</v>
       </c>
       <c r="B73" t="n">
-        <v>98206</v>
+        <v>98197</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483452</v>
+        <v>483206</v>
       </c>
       <c r="R73" t="n">
-        <v>6948488</v>
+        <v>6948535</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178685</v>
+        <v>122178688</v>
       </c>
       <c r="B74" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483448</v>
+        <v>483425</v>
       </c>
       <c r="R74" t="n">
-        <v>6948530</v>
+        <v>6948524</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178703</v>
+        <v>122178725</v>
       </c>
       <c r="B75" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483313</v>
+        <v>483174</v>
       </c>
       <c r="R75" t="n">
-        <v>6948690</v>
+        <v>6948830</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178703</v>
+        <v>122178676</v>
       </c>
       <c r="B41" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483313</v>
+        <v>483258</v>
       </c>
       <c r="R41" t="n">
-        <v>6948690</v>
+        <v>6948497</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178726</v>
+        <v>122178682</v>
       </c>
       <c r="B42" t="n">
-        <v>78388</v>
+        <v>98223</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483017</v>
+        <v>483452</v>
       </c>
       <c r="R42" t="n">
-        <v>6948711</v>
+        <v>6948488</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178685</v>
+        <v>122178727</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483448</v>
+        <v>482951</v>
       </c>
       <c r="R43" t="n">
-        <v>6948530</v>
+        <v>6948660</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178686</v>
+        <v>122178672</v>
       </c>
       <c r="B44" t="n">
-        <v>98218</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483445</v>
+        <v>483111</v>
       </c>
       <c r="R44" t="n">
-        <v>6948521</v>
+        <v>6948568</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178673</v>
+        <v>122178688</v>
       </c>
       <c r="B45" t="n">
-        <v>97151</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483127</v>
+        <v>483425</v>
       </c>
       <c r="R45" t="n">
-        <v>6948551</v>
+        <v>6948524</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178679</v>
+        <v>122178726</v>
       </c>
       <c r="B46" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483412</v>
+        <v>483017</v>
       </c>
       <c r="R46" t="n">
-        <v>6948450</v>
+        <v>6948711</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178699</v>
+        <v>122178692</v>
       </c>
       <c r="B47" t="n">
-        <v>98197</v>
+        <v>97156</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483311</v>
+        <v>483406</v>
       </c>
       <c r="R47" t="n">
-        <v>6948661</v>
+        <v>6948521</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178692</v>
+        <v>122178677</v>
       </c>
       <c r="B48" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483406</v>
+        <v>483297</v>
       </c>
       <c r="R48" t="n">
-        <v>6948521</v>
+        <v>6948492</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178682</v>
+        <v>122178695</v>
       </c>
       <c r="B49" t="n">
-        <v>98218</v>
+        <v>78651</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483452</v>
+        <v>483360</v>
       </c>
       <c r="R49" t="n">
-        <v>6948488</v>
+        <v>6948597</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178694</v>
+        <v>122178683</v>
       </c>
       <c r="B50" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6055,25 +6055,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483393</v>
+        <v>483448</v>
       </c>
       <c r="R50" t="n">
-        <v>6948545</v>
+        <v>6948496</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178689</v>
+        <v>122178674</v>
       </c>
       <c r="B51" t="n">
-        <v>79732</v>
+        <v>98202</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483427</v>
+        <v>483168</v>
       </c>
       <c r="R51" t="n">
-        <v>6948511</v>
+        <v>6948539</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178681</v>
+        <v>122178669</v>
       </c>
       <c r="B52" t="n">
-        <v>78387</v>
+        <v>98223</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6259,25 +6259,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483465</v>
+        <v>482972</v>
       </c>
       <c r="R52" t="n">
-        <v>6948486</v>
+        <v>6948524</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178678</v>
+        <v>122178689</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79732</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,25 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483411</v>
+        <v>483427</v>
       </c>
       <c r="R53" t="n">
-        <v>6948445</v>
+        <v>6948511</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178676</v>
+        <v>122178680</v>
       </c>
       <c r="B54" t="n">
-        <v>78651</v>
+        <v>79636</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483258</v>
+        <v>483471</v>
       </c>
       <c r="R54" t="n">
-        <v>6948497</v>
+        <v>6948473</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178701</v>
+        <v>122178684</v>
       </c>
       <c r="B55" t="n">
         <v>79732</v>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483306</v>
+        <v>483433</v>
       </c>
       <c r="R55" t="n">
-        <v>6948674</v>
+        <v>6948515</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178677</v>
+        <v>122178693</v>
       </c>
       <c r="B56" t="n">
-        <v>97151</v>
+        <v>98223</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483297</v>
+        <v>483400</v>
       </c>
       <c r="R56" t="n">
-        <v>6948492</v>
+        <v>6948533</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178702</v>
+        <v>122178679</v>
       </c>
       <c r="B57" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483308</v>
+        <v>483412</v>
       </c>
       <c r="R57" t="n">
-        <v>6948678</v>
+        <v>6948450</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178669</v>
+        <v>122178681</v>
       </c>
       <c r="B58" t="n">
-        <v>98218</v>
+        <v>78387</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482972</v>
+        <v>483465</v>
       </c>
       <c r="R58" t="n">
-        <v>6948524</v>
+        <v>6948486</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178671</v>
+        <v>122178701</v>
       </c>
       <c r="B59" t="n">
-        <v>78388</v>
+        <v>79732</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483025</v>
+        <v>483306</v>
       </c>
       <c r="R59" t="n">
-        <v>6948533</v>
+        <v>6948674</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178695</v>
+        <v>122178700</v>
       </c>
       <c r="B60" t="n">
-        <v>78651</v>
+        <v>98223</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483360</v>
+        <v>483303</v>
       </c>
       <c r="R60" t="n">
-        <v>6948597</v>
+        <v>6948673</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178674</v>
+        <v>122178725</v>
       </c>
       <c r="B61" t="n">
-        <v>98197</v>
+        <v>97156</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483168</v>
+        <v>483174</v>
       </c>
       <c r="R61" t="n">
-        <v>6948539</v>
+        <v>6948830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178700</v>
+        <v>122178675</v>
       </c>
       <c r="B62" t="n">
-        <v>98218</v>
+        <v>98202</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483303</v>
+        <v>483206</v>
       </c>
       <c r="R62" t="n">
-        <v>6948673</v>
+        <v>6948535</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178693</v>
+        <v>122178694</v>
       </c>
       <c r="B63" t="n">
-        <v>98218</v>
+        <v>78651</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483400</v>
+        <v>483393</v>
       </c>
       <c r="R63" t="n">
-        <v>6948533</v>
+        <v>6948545</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178698</v>
+        <v>122178687</v>
       </c>
       <c r="B64" t="n">
-        <v>98197</v>
+        <v>79732</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7483,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483316</v>
+        <v>483437</v>
       </c>
       <c r="R64" t="n">
-        <v>6948659</v>
+        <v>6948523</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178727</v>
+        <v>122178671</v>
       </c>
       <c r="B65" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>482951</v>
+        <v>483025</v>
       </c>
       <c r="R65" t="n">
-        <v>6948660</v>
+        <v>6948533</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178687</v>
+        <v>122178686</v>
       </c>
       <c r="B66" t="n">
-        <v>79732</v>
+        <v>98223</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483437</v>
+        <v>483445</v>
       </c>
       <c r="R66" t="n">
-        <v>6948523</v>
+        <v>6948521</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178691</v>
+        <v>122178697</v>
       </c>
       <c r="B67" t="n">
-        <v>98114</v>
+        <v>97156</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483406</v>
+        <v>483357</v>
       </c>
       <c r="R67" t="n">
-        <v>6948521</v>
+        <v>6948607</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178680</v>
+        <v>122178685</v>
       </c>
       <c r="B68" t="n">
-        <v>79636</v>
+        <v>79732</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7891,25 +7891,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483471</v>
+        <v>483448</v>
       </c>
       <c r="R68" t="n">
-        <v>6948473</v>
+        <v>6948530</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178683</v>
+        <v>122178699</v>
       </c>
       <c r="B69" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483448</v>
+        <v>483311</v>
       </c>
       <c r="R69" t="n">
-        <v>6948496</v>
+        <v>6948661</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178684</v>
+        <v>122178678</v>
       </c>
       <c r="B70" t="n">
-        <v>79732</v>
+        <v>98106</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483433</v>
+        <v>483411</v>
       </c>
       <c r="R70" t="n">
-        <v>6948515</v>
+        <v>6948445</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178672</v>
+        <v>122178703</v>
       </c>
       <c r="B71" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8201,21 +8201,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483111</v>
+        <v>483313</v>
       </c>
       <c r="R71" t="n">
-        <v>6948568</v>
+        <v>6948690</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178697</v>
+        <v>122178673</v>
       </c>
       <c r="B72" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483357</v>
+        <v>483127</v>
       </c>
       <c r="R72" t="n">
-        <v>6948607</v>
+        <v>6948551</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178675</v>
+        <v>122178691</v>
       </c>
       <c r="B73" t="n">
-        <v>98197</v>
+        <v>98119</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483206</v>
+        <v>483406</v>
       </c>
       <c r="R73" t="n">
-        <v>6948535</v>
+        <v>6948521</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178688</v>
+        <v>122178698</v>
       </c>
       <c r="B74" t="n">
-        <v>79732</v>
+        <v>98202</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483425</v>
+        <v>483316</v>
       </c>
       <c r="R74" t="n">
-        <v>6948524</v>
+        <v>6948659</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178725</v>
+        <v>122178702</v>
       </c>
       <c r="B75" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483174</v>
+        <v>483308</v>
       </c>
       <c r="R75" t="n">
-        <v>6948830</v>
+        <v>6948678</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178700</v>
+        <v>122178725</v>
       </c>
       <c r="B60" t="n">
-        <v>98223</v>
+        <v>97156</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483303</v>
+        <v>483174</v>
       </c>
       <c r="R60" t="n">
-        <v>6948673</v>
+        <v>6948830</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178725</v>
+        <v>122178700</v>
       </c>
       <c r="B61" t="n">
-        <v>97156</v>
+        <v>98223</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7181,21 +7181,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483174</v>
+        <v>483303</v>
       </c>
       <c r="R61" t="n">
-        <v>6948830</v>
+        <v>6948673</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178676</v>
+        <v>122178689</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5141,21 +5141,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5160,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483258</v>
+        <v>483427</v>
       </c>
       <c r="R41" t="n">
-        <v>6948497</v>
+        <v>6948511</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178682</v>
+        <v>122178693</v>
       </c>
       <c r="B42" t="n">
-        <v>98223</v>
+        <v>98232</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5245,11 +5240,6 @@
       <c r="E42" t="n">
         <v>221952</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Neottia cordata</t>
@@ -5267,10 +5257,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483452</v>
+        <v>483400</v>
       </c>
       <c r="R42" t="n">
-        <v>6948488</v>
+        <v>6948533</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5319,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178727</v>
+        <v>122178726</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5335,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5354,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482951</v>
+        <v>483017</v>
       </c>
       <c r="R43" t="n">
-        <v>6948660</v>
+        <v>6948711</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5416,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178672</v>
+        <v>122178695</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5449,11 +5434,6 @@
       <c r="E44" t="n">
         <v>6425</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5471,10 +5451,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483111</v>
+        <v>483360</v>
       </c>
       <c r="R44" t="n">
-        <v>6948568</v>
+        <v>6948597</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178688</v>
+        <v>122178681</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>78388</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5549,21 +5529,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5548,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483425</v>
+        <v>483465</v>
       </c>
       <c r="R45" t="n">
-        <v>6948524</v>
+        <v>6948486</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178726</v>
+        <v>122178698</v>
       </c>
       <c r="B46" t="n">
-        <v>78388</v>
+        <v>98211</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5622,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5645,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483017</v>
+        <v>483316</v>
       </c>
       <c r="R46" t="n">
-        <v>6948711</v>
+        <v>6948659</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5707,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178692</v>
+        <v>122178700</v>
       </c>
       <c r="B47" t="n">
-        <v>97156</v>
+        <v>98232</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,21 +5723,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5742,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483406</v>
+        <v>483303</v>
       </c>
       <c r="R47" t="n">
-        <v>6948521</v>
+        <v>6948673</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178677</v>
+        <v>122178673</v>
       </c>
       <c r="B48" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5857,11 +5822,6 @@
       <c r="E48" t="n">
         <v>221945</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -5879,10 +5839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483297</v>
+        <v>483127</v>
       </c>
       <c r="R48" t="n">
-        <v>6948492</v>
+        <v>6948551</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5901,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178695</v>
+        <v>122178697</v>
       </c>
       <c r="B49" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5913,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5936,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483360</v>
+        <v>483357</v>
       </c>
       <c r="R49" t="n">
-        <v>6948597</v>
+        <v>6948607</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +5998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178683</v>
+        <v>122178701</v>
       </c>
       <c r="B50" t="n">
-        <v>98202</v>
+        <v>79733</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6055,25 +6010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6033,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483448</v>
+        <v>483306</v>
       </c>
       <c r="R50" t="n">
-        <v>6948496</v>
+        <v>6948674</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6095,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178674</v>
+        <v>122178703</v>
       </c>
       <c r="B51" t="n">
-        <v>98202</v>
+        <v>79733</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6107,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6130,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483168</v>
+        <v>483313</v>
       </c>
       <c r="R51" t="n">
-        <v>6948539</v>
+        <v>6948690</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6192,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178669</v>
+        <v>122178685</v>
       </c>
       <c r="B52" t="n">
-        <v>98223</v>
+        <v>79733</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6259,25 +6204,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6227,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>482972</v>
+        <v>483448</v>
       </c>
       <c r="R52" t="n">
-        <v>6948524</v>
+        <v>6948530</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6289,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178689</v>
+        <v>122178694</v>
       </c>
       <c r="B53" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6365,21 +6305,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6324,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483427</v>
+        <v>483393</v>
       </c>
       <c r="R53" t="n">
-        <v>6948511</v>
+        <v>6948545</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6386,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178680</v>
+        <v>122178682</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>98232</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6467,21 +6402,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6421,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483471</v>
+        <v>483452</v>
       </c>
       <c r="R54" t="n">
-        <v>6948473</v>
+        <v>6948488</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,10 +6483,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178684</v>
+        <v>122178725</v>
       </c>
       <c r="B55" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6495,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6518,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483433</v>
+        <v>483174</v>
       </c>
       <c r="R55" t="n">
-        <v>6948515</v>
+        <v>6948830</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178693</v>
+        <v>122178686</v>
       </c>
       <c r="B56" t="n">
-        <v>98223</v>
+        <v>98232</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6673,11 +6598,6 @@
       <c r="E56" t="n">
         <v>221952</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Neottia cordata</t>
@@ -6695,10 +6615,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483400</v>
+        <v>483445</v>
       </c>
       <c r="R56" t="n">
-        <v>6948533</v>
+        <v>6948521</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6677,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178679</v>
+        <v>122178702</v>
       </c>
       <c r="B57" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6689,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6712,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483412</v>
+        <v>483308</v>
       </c>
       <c r="R57" t="n">
-        <v>6948450</v>
+        <v>6948678</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6774,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178681</v>
+        <v>122178680</v>
       </c>
       <c r="B58" t="n">
-        <v>78387</v>
+        <v>79637</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6786,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>6456</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6809,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483465</v>
+        <v>483471</v>
       </c>
       <c r="R58" t="n">
-        <v>6948486</v>
+        <v>6948473</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6871,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178701</v>
+        <v>122178688</v>
       </c>
       <c r="B59" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6979,11 +6889,6 @@
       <c r="E59" t="n">
         <v>6458</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7001,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483306</v>
+        <v>483425</v>
       </c>
       <c r="R59" t="n">
-        <v>6948674</v>
+        <v>6948524</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +6968,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178725</v>
+        <v>122178672</v>
       </c>
       <c r="B60" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +6980,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7003,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483174</v>
+        <v>483111</v>
       </c>
       <c r="R60" t="n">
-        <v>6948830</v>
+        <v>6948568</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7065,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178700</v>
+        <v>122178727</v>
       </c>
       <c r="B61" t="n">
-        <v>98223</v>
+        <v>78652</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7077,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7100,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483303</v>
+        <v>482951</v>
       </c>
       <c r="R61" t="n">
-        <v>6948673</v>
+        <v>6948660</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7270,7 +7165,7 @@
         <v>122178675</v>
       </c>
       <c r="B62" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7284,11 +7179,6 @@
       </c>
       <c r="E62" t="n">
         <v>220787</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7369,10 +7259,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178694</v>
+        <v>122178683</v>
       </c>
       <c r="B63" t="n">
-        <v>78651</v>
+        <v>98211</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7381,25 +7271,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7294,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483393</v>
+        <v>483448</v>
       </c>
       <c r="R63" t="n">
-        <v>6948545</v>
+        <v>6948496</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7356,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178687</v>
+        <v>122178677</v>
       </c>
       <c r="B64" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7368,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7391,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483437</v>
+        <v>483297</v>
       </c>
       <c r="R64" t="n">
-        <v>6948523</v>
+        <v>6948492</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7576,7 +7456,7 @@
         <v>122178671</v>
       </c>
       <c r="B65" t="n">
-        <v>78388</v>
+        <v>78389</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7590,11 +7470,6 @@
       </c>
       <c r="E65" t="n">
         <v>228912</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7675,10 +7550,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178686</v>
+        <v>122178679</v>
       </c>
       <c r="B66" t="n">
-        <v>98223</v>
+        <v>78652</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7562,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483445</v>
+        <v>483412</v>
       </c>
       <c r="R66" t="n">
-        <v>6948521</v>
+        <v>6948450</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7647,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178697</v>
+        <v>122178676</v>
       </c>
       <c r="B67" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7789,25 +7659,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7682,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483357</v>
+        <v>483258</v>
       </c>
       <c r="R67" t="n">
-        <v>6948607</v>
+        <v>6948497</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7744,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178685</v>
+        <v>122178684</v>
       </c>
       <c r="B68" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7897,11 +7762,6 @@
       <c r="E68" t="n">
         <v>6458</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7919,10 +7779,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483448</v>
+        <v>483433</v>
       </c>
       <c r="R68" t="n">
-        <v>6948530</v>
+        <v>6948515</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7841,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178699</v>
+        <v>122178678</v>
       </c>
       <c r="B69" t="n">
-        <v>98202</v>
+        <v>98115</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7853,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +7876,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483311</v>
+        <v>483411</v>
       </c>
       <c r="R69" t="n">
-        <v>6948661</v>
+        <v>6948445</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +7938,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178678</v>
+        <v>122178674</v>
       </c>
       <c r="B70" t="n">
-        <v>98106</v>
+        <v>98211</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +7950,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +7973,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483411</v>
+        <v>483168</v>
       </c>
       <c r="R70" t="n">
-        <v>6948445</v>
+        <v>6948539</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8035,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178703</v>
+        <v>122178687</v>
       </c>
       <c r="B71" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8203,11 +8053,6 @@
       <c r="E71" t="n">
         <v>6458</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8225,10 +8070,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483313</v>
+        <v>483437</v>
       </c>
       <c r="R71" t="n">
-        <v>6948690</v>
+        <v>6948523</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8132,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178673</v>
+        <v>122178669</v>
       </c>
       <c r="B72" t="n">
-        <v>97156</v>
+        <v>98232</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8303,21 +8148,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8167,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483127</v>
+        <v>482972</v>
       </c>
       <c r="R72" t="n">
-        <v>6948551</v>
+        <v>6948524</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,10 +8229,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178691</v>
+        <v>122178692</v>
       </c>
       <c r="B73" t="n">
-        <v>98119</v>
+        <v>97165</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8405,21 +8245,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8491,10 +8326,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178698</v>
+        <v>122178691</v>
       </c>
       <c r="B74" t="n">
-        <v>98202</v>
+        <v>98128</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8338,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>219790</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8361,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483316</v>
+        <v>483406</v>
       </c>
       <c r="R74" t="n">
-        <v>6948659</v>
+        <v>6948521</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178702</v>
+        <v>122178699</v>
       </c>
       <c r="B75" t="n">
-        <v>97156</v>
+        <v>98211</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8435,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8458,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483308</v>
+        <v>483311</v>
       </c>
       <c r="R75" t="n">
-        <v>6948678</v>
+        <v>6948661</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178681</v>
+        <v>122178700</v>
       </c>
       <c r="B45" t="n">
-        <v>78388</v>
+        <v>98232</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5525,20 +5525,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483465</v>
+        <v>483303</v>
       </c>
       <c r="R45" t="n">
-        <v>6948486</v>
+        <v>6948673</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5610,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178698</v>
+        <v>122178673</v>
       </c>
       <c r="B46" t="n">
-        <v>98211</v>
+        <v>97165</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5622,20 +5622,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483316</v>
+        <v>483127</v>
       </c>
       <c r="R46" t="n">
-        <v>6948659</v>
+        <v>6948551</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178700</v>
+        <v>122178697</v>
       </c>
       <c r="B47" t="n">
-        <v>98232</v>
+        <v>97165</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483303</v>
+        <v>483357</v>
       </c>
       <c r="R47" t="n">
-        <v>6948673</v>
+        <v>6948607</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5804,10 +5804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178673</v>
+        <v>122178681</v>
       </c>
       <c r="B48" t="n">
-        <v>97165</v>
+        <v>78388</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5816,20 +5816,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483127</v>
+        <v>483465</v>
       </c>
       <c r="R48" t="n">
-        <v>6948551</v>
+        <v>6948486</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178697</v>
+        <v>122178698</v>
       </c>
       <c r="B49" t="n">
-        <v>97165</v>
+        <v>98211</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5913,20 +5913,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483357</v>
+        <v>483316</v>
       </c>
       <c r="R49" t="n">
-        <v>6948607</v>
+        <v>6948659</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7065,10 +7065,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178727</v>
+        <v>122178675</v>
       </c>
       <c r="B61" t="n">
-        <v>78652</v>
+        <v>98211</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7077,20 +7077,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7100,10 +7100,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>482951</v>
+        <v>483206</v>
       </c>
       <c r="R61" t="n">
-        <v>6948660</v>
+        <v>6948535</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7162,10 +7162,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178675</v>
+        <v>122178727</v>
       </c>
       <c r="B62" t="n">
-        <v>98211</v>
+        <v>78652</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483206</v>
+        <v>482951</v>
       </c>
       <c r="R62" t="n">
-        <v>6948535</v>
+        <v>6948660</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5513,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178700</v>
+        <v>122178681</v>
       </c>
       <c r="B45" t="n">
-        <v>98232</v>
+        <v>78388</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5525,20 +5525,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483303</v>
+        <v>483465</v>
       </c>
       <c r="R45" t="n">
-        <v>6948673</v>
+        <v>6948486</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5610,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178673</v>
+        <v>122178698</v>
       </c>
       <c r="B46" t="n">
-        <v>97165</v>
+        <v>98211</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5622,20 +5622,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483127</v>
+        <v>483316</v>
       </c>
       <c r="R46" t="n">
-        <v>6948551</v>
+        <v>6948659</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178697</v>
+        <v>122178700</v>
       </c>
       <c r="B47" t="n">
-        <v>97165</v>
+        <v>98232</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483357</v>
+        <v>483303</v>
       </c>
       <c r="R47" t="n">
-        <v>6948607</v>
+        <v>6948673</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5804,10 +5804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178681</v>
+        <v>122178673</v>
       </c>
       <c r="B48" t="n">
-        <v>78388</v>
+        <v>97165</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5816,20 +5816,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483465</v>
+        <v>483127</v>
       </c>
       <c r="R48" t="n">
-        <v>6948486</v>
+        <v>6948551</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178698</v>
+        <v>122178697</v>
       </c>
       <c r="B49" t="n">
-        <v>98211</v>
+        <v>97165</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5913,20 +5913,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483316</v>
+        <v>483357</v>
       </c>
       <c r="R49" t="n">
-        <v>6948659</v>
+        <v>6948607</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -7065,10 +7065,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178675</v>
+        <v>122178727</v>
       </c>
       <c r="B61" t="n">
-        <v>98211</v>
+        <v>78652</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7077,20 +7077,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7100,10 +7100,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483206</v>
+        <v>482951</v>
       </c>
       <c r="R61" t="n">
-        <v>6948535</v>
+        <v>6948660</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7162,10 +7162,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178727</v>
+        <v>122178675</v>
       </c>
       <c r="B62" t="n">
-        <v>78652</v>
+        <v>98211</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7174,20 +7174,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>482951</v>
+        <v>483206</v>
       </c>
       <c r="R62" t="n">
-        <v>6948660</v>
+        <v>6948535</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178689</v>
+        <v>122178702</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>97178</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,20 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5160,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483427</v>
+        <v>483308</v>
       </c>
       <c r="R41" t="n">
-        <v>6948511</v>
+        <v>6948678</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5222,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178693</v>
+        <v>122178695</v>
       </c>
       <c r="B42" t="n">
-        <v>98232</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5234,20 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5257,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483400</v>
+        <v>483360</v>
       </c>
       <c r="R42" t="n">
-        <v>6948533</v>
+        <v>6948597</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5319,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178726</v>
+        <v>122178703</v>
       </c>
       <c r="B43" t="n">
-        <v>78389</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5335,16 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5354,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483017</v>
+        <v>483313</v>
       </c>
       <c r="R43" t="n">
-        <v>6948711</v>
+        <v>6948690</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5416,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178695</v>
+        <v>122178687</v>
       </c>
       <c r="B44" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,16 +5447,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483360</v>
+        <v>483437</v>
       </c>
       <c r="R44" t="n">
-        <v>6948597</v>
+        <v>6948523</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5513,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178681</v>
+        <v>122178680</v>
       </c>
       <c r="B45" t="n">
-        <v>78388</v>
+        <v>79641</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5525,20 +5545,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6456</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5548,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483465</v>
+        <v>483471</v>
       </c>
       <c r="R45" t="n">
-        <v>6948486</v>
+        <v>6948473</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5610,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178698</v>
+        <v>122178726</v>
       </c>
       <c r="B46" t="n">
-        <v>98211</v>
+        <v>78393</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5622,20 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5645,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483316</v>
+        <v>483017</v>
       </c>
       <c r="R46" t="n">
-        <v>6948659</v>
+        <v>6948711</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5710,7 +5740,7 @@
         <v>122178700</v>
       </c>
       <c r="B47" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5724,6 +5754,11 @@
       </c>
       <c r="E47" t="n">
         <v>221952</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5804,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178673</v>
+        <v>122178692</v>
       </c>
       <c r="B48" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5822,6 +5857,11 @@
       <c r="E48" t="n">
         <v>221945</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -5839,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483127</v>
+        <v>483406</v>
       </c>
       <c r="R48" t="n">
-        <v>6948551</v>
+        <v>6948521</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5901,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178697</v>
+        <v>122178675</v>
       </c>
       <c r="B49" t="n">
-        <v>97165</v>
+        <v>98224</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5913,20 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5936,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483357</v>
+        <v>483206</v>
       </c>
       <c r="R49" t="n">
-        <v>6948607</v>
+        <v>6948535</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178701</v>
+        <v>122178672</v>
       </c>
       <c r="B50" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6014,16 +6059,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6033,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483306</v>
+        <v>483111</v>
       </c>
       <c r="R50" t="n">
-        <v>6948674</v>
+        <v>6948568</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6095,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178703</v>
+        <v>122178688</v>
       </c>
       <c r="B51" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6113,6 +6163,11 @@
       <c r="E51" t="n">
         <v>6458</v>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -6130,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483313</v>
+        <v>483425</v>
       </c>
       <c r="R51" t="n">
-        <v>6948690</v>
+        <v>6948524</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6192,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178685</v>
+        <v>122178673</v>
       </c>
       <c r="B52" t="n">
-        <v>79733</v>
+        <v>97178</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6204,20 +6259,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6227,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483448</v>
+        <v>483127</v>
       </c>
       <c r="R52" t="n">
-        <v>6948530</v>
+        <v>6948551</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6289,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178694</v>
+        <v>122178669</v>
       </c>
       <c r="B53" t="n">
-        <v>78652</v>
+        <v>98245</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6301,20 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6324,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483393</v>
+        <v>482972</v>
       </c>
       <c r="R53" t="n">
-        <v>6948545</v>
+        <v>6948524</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6386,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178682</v>
+        <v>122178683</v>
       </c>
       <c r="B54" t="n">
-        <v>98232</v>
+        <v>98224</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6398,20 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6421,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483452</v>
+        <v>483448</v>
       </c>
       <c r="R54" t="n">
-        <v>6948488</v>
+        <v>6948496</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6483,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178725</v>
+        <v>122178674</v>
       </c>
       <c r="B55" t="n">
-        <v>97165</v>
+        <v>98224</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6495,20 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6518,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483174</v>
+        <v>483168</v>
       </c>
       <c r="R55" t="n">
-        <v>6948830</v>
+        <v>6948539</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6580,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178686</v>
+        <v>122178684</v>
       </c>
       <c r="B56" t="n">
-        <v>98232</v>
+        <v>79737</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6592,20 +6667,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6615,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483445</v>
+        <v>483433</v>
       </c>
       <c r="R56" t="n">
-        <v>6948521</v>
+        <v>6948515</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6677,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178702</v>
+        <v>122178682</v>
       </c>
       <c r="B57" t="n">
-        <v>97165</v>
+        <v>98245</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6693,16 +6773,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6712,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483308</v>
+        <v>483452</v>
       </c>
       <c r="R57" t="n">
-        <v>6948678</v>
+        <v>6948488</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6774,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178680</v>
+        <v>122178697</v>
       </c>
       <c r="B58" t="n">
-        <v>79637</v>
+        <v>97178</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6790,16 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>221945</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6809,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483471</v>
+        <v>483357</v>
       </c>
       <c r="R58" t="n">
-        <v>6948473</v>
+        <v>6948607</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6871,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178688</v>
+        <v>122178671</v>
       </c>
       <c r="B59" t="n">
-        <v>79733</v>
+        <v>78393</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6887,16 +6977,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483425</v>
+        <v>483025</v>
       </c>
       <c r="R59" t="n">
-        <v>6948524</v>
+        <v>6948533</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6968,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178672</v>
+        <v>122178694</v>
       </c>
       <c r="B60" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6986,6 +7081,11 @@
       <c r="E60" t="n">
         <v>6425</v>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -7003,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483111</v>
+        <v>483393</v>
       </c>
       <c r="R60" t="n">
-        <v>6948568</v>
+        <v>6948545</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7065,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178727</v>
+        <v>122178725</v>
       </c>
       <c r="B61" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7077,20 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7100,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>482951</v>
+        <v>483174</v>
       </c>
       <c r="R61" t="n">
-        <v>6948660</v>
+        <v>6948830</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7162,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178675</v>
+        <v>122178685</v>
       </c>
       <c r="B62" t="n">
-        <v>98211</v>
+        <v>79737</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7174,20 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7197,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483206</v>
+        <v>483448</v>
       </c>
       <c r="R62" t="n">
-        <v>6948535</v>
+        <v>6948530</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7259,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178683</v>
+        <v>122178681</v>
       </c>
       <c r="B63" t="n">
-        <v>98211</v>
+        <v>78392</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7271,20 +7381,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7294,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483448</v>
+        <v>483465</v>
       </c>
       <c r="R63" t="n">
-        <v>6948496</v>
+        <v>6948486</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7356,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178677</v>
+        <v>122178691</v>
       </c>
       <c r="B64" t="n">
-        <v>97165</v>
+        <v>98141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7372,16 +7487,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>219790</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7391,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483297</v>
+        <v>483406</v>
       </c>
       <c r="R64" t="n">
-        <v>6948492</v>
+        <v>6948521</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7453,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178671</v>
+        <v>122178677</v>
       </c>
       <c r="B65" t="n">
-        <v>78389</v>
+        <v>97178</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7465,20 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>221945</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7488,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483025</v>
+        <v>483297</v>
       </c>
       <c r="R65" t="n">
-        <v>6948533</v>
+        <v>6948492</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7550,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178679</v>
+        <v>122178698</v>
       </c>
       <c r="B66" t="n">
-        <v>78652</v>
+        <v>98224</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7562,20 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7585,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483412</v>
+        <v>483316</v>
       </c>
       <c r="R66" t="n">
-        <v>6948450</v>
+        <v>6948659</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7650,7 +7780,7 @@
         <v>122178676</v>
       </c>
       <c r="B67" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7664,6 +7794,11 @@
       </c>
       <c r="E67" t="n">
         <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -7744,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178684</v>
+        <v>122178689</v>
       </c>
       <c r="B68" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7762,6 +7897,11 @@
       <c r="E68" t="n">
         <v>6458</v>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7779,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483433</v>
+        <v>483427</v>
       </c>
       <c r="R68" t="n">
-        <v>6948515</v>
+        <v>6948511</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7844,7 +7984,7 @@
         <v>122178678</v>
       </c>
       <c r="B69" t="n">
-        <v>98115</v>
+        <v>98128</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7858,6 +7998,11 @@
       </c>
       <c r="E69" t="n">
         <v>220093</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -7938,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178674</v>
+        <v>122178693</v>
       </c>
       <c r="B70" t="n">
-        <v>98211</v>
+        <v>98245</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7950,20 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221952</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7973,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483168</v>
+        <v>483400</v>
       </c>
       <c r="R70" t="n">
-        <v>6948539</v>
+        <v>6948533</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8035,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178687</v>
+        <v>122178699</v>
       </c>
       <c r="B71" t="n">
-        <v>79733</v>
+        <v>98224</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8047,20 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8070,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483437</v>
+        <v>483311</v>
       </c>
       <c r="R71" t="n">
-        <v>6948523</v>
+        <v>6948661</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8132,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178669</v>
+        <v>122178727</v>
       </c>
       <c r="B72" t="n">
-        <v>98232</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8144,20 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8167,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482972</v>
+        <v>482951</v>
       </c>
       <c r="R72" t="n">
-        <v>6948524</v>
+        <v>6948660</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8229,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178692</v>
+        <v>122178701</v>
       </c>
       <c r="B73" t="n">
-        <v>97165</v>
+        <v>79737</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8241,20 +8401,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8264,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483406</v>
+        <v>483306</v>
       </c>
       <c r="R73" t="n">
-        <v>6948521</v>
+        <v>6948674</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8326,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178691</v>
+        <v>122178686</v>
       </c>
       <c r="B74" t="n">
-        <v>98128</v>
+        <v>98245</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8342,16 +8507,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8361,7 +8531,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483406</v>
+        <v>483445</v>
       </c>
       <c r="R74" t="n">
         <v>6948521</v>
@@ -8423,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178699</v>
+        <v>122178679</v>
       </c>
       <c r="B75" t="n">
-        <v>98211</v>
+        <v>78656</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8435,20 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8458,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483311</v>
+        <v>483412</v>
       </c>
       <c r="R75" t="n">
-        <v>6948661</v>
+        <v>6948450</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178702</v>
+        <v>122178685</v>
       </c>
       <c r="B41" t="n">
-        <v>97178</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483308</v>
+        <v>483448</v>
       </c>
       <c r="R41" t="n">
-        <v>6948678</v>
+        <v>6948530</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178695</v>
+        <v>122178703</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483360</v>
+        <v>483313</v>
       </c>
       <c r="R42" t="n">
-        <v>6948597</v>
+        <v>6948690</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178703</v>
+        <v>122178672</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483313</v>
+        <v>483111</v>
       </c>
       <c r="R43" t="n">
-        <v>6948690</v>
+        <v>6948568</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178687</v>
+        <v>122178698</v>
       </c>
       <c r="B44" t="n">
-        <v>79737</v>
+        <v>98237</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483437</v>
+        <v>483316</v>
       </c>
       <c r="R44" t="n">
-        <v>6948523</v>
+        <v>6948659</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178680</v>
+        <v>122178677</v>
       </c>
       <c r="B45" t="n">
-        <v>79641</v>
+        <v>97191</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5549,21 +5549,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483471</v>
+        <v>483297</v>
       </c>
       <c r="R45" t="n">
-        <v>6948473</v>
+        <v>6948492</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178726</v>
+        <v>122178669</v>
       </c>
       <c r="B46" t="n">
-        <v>78393</v>
+        <v>98258</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483017</v>
+        <v>482972</v>
       </c>
       <c r="R46" t="n">
-        <v>6948711</v>
+        <v>6948524</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178700</v>
+        <v>122178725</v>
       </c>
       <c r="B47" t="n">
-        <v>98245</v>
+        <v>97191</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,21 +5753,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483303</v>
+        <v>483174</v>
       </c>
       <c r="R47" t="n">
-        <v>6948673</v>
+        <v>6948830</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178692</v>
+        <v>122178726</v>
       </c>
       <c r="B48" t="n">
-        <v>97178</v>
+        <v>78393</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483406</v>
+        <v>483017</v>
       </c>
       <c r="R48" t="n">
-        <v>6948521</v>
+        <v>6948711</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178675</v>
+        <v>122178676</v>
       </c>
       <c r="B49" t="n">
-        <v>98224</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483206</v>
+        <v>483258</v>
       </c>
       <c r="R49" t="n">
-        <v>6948535</v>
+        <v>6948497</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178672</v>
+        <v>122178727</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483111</v>
+        <v>482951</v>
       </c>
       <c r="R50" t="n">
-        <v>6948568</v>
+        <v>6948660</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178688</v>
+        <v>122178694</v>
       </c>
       <c r="B51" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6161,21 +6161,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483425</v>
+        <v>483393</v>
       </c>
       <c r="R51" t="n">
-        <v>6948524</v>
+        <v>6948545</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178673</v>
+        <v>122178686</v>
       </c>
       <c r="B52" t="n">
-        <v>97178</v>
+        <v>98258</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6263,21 +6263,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483127</v>
+        <v>483445</v>
       </c>
       <c r="R52" t="n">
-        <v>6948551</v>
+        <v>6948521</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178669</v>
+        <v>122178688</v>
       </c>
       <c r="B53" t="n">
-        <v>98245</v>
+        <v>79737</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,25 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>482972</v>
+        <v>483425</v>
       </c>
       <c r="R53" t="n">
         <v>6948524</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178683</v>
+        <v>122178671</v>
       </c>
       <c r="B54" t="n">
-        <v>98224</v>
+        <v>78393</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483448</v>
+        <v>483025</v>
       </c>
       <c r="R54" t="n">
-        <v>6948496</v>
+        <v>6948533</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178674</v>
+        <v>122178702</v>
       </c>
       <c r="B55" t="n">
-        <v>98224</v>
+        <v>97191</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483168</v>
+        <v>483308</v>
       </c>
       <c r="R55" t="n">
-        <v>6948539</v>
+        <v>6948678</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178684</v>
+        <v>122178679</v>
       </c>
       <c r="B56" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483433</v>
+        <v>483412</v>
       </c>
       <c r="R56" t="n">
-        <v>6948515</v>
+        <v>6948450</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178682</v>
+        <v>122178681</v>
       </c>
       <c r="B57" t="n">
-        <v>98245</v>
+        <v>78392</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483452</v>
+        <v>483465</v>
       </c>
       <c r="R57" t="n">
-        <v>6948488</v>
+        <v>6948486</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178697</v>
+        <v>122178674</v>
       </c>
       <c r="B58" t="n">
-        <v>97178</v>
+        <v>98237</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483357</v>
+        <v>483168</v>
       </c>
       <c r="R58" t="n">
-        <v>6948607</v>
+        <v>6948539</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178671</v>
+        <v>122178678</v>
       </c>
       <c r="B59" t="n">
-        <v>78393</v>
+        <v>98141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6973,25 +6973,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483025</v>
+        <v>483411</v>
       </c>
       <c r="R59" t="n">
-        <v>6948533</v>
+        <v>6948445</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178694</v>
+        <v>122178675</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483393</v>
+        <v>483206</v>
       </c>
       <c r="R60" t="n">
-        <v>6948545</v>
+        <v>6948535</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178725</v>
+        <v>122178692</v>
       </c>
       <c r="B61" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483174</v>
+        <v>483406</v>
       </c>
       <c r="R61" t="n">
-        <v>6948830</v>
+        <v>6948521</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178685</v>
+        <v>122178673</v>
       </c>
       <c r="B62" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483448</v>
+        <v>483127</v>
       </c>
       <c r="R62" t="n">
-        <v>6948530</v>
+        <v>6948551</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178681</v>
+        <v>122178691</v>
       </c>
       <c r="B63" t="n">
-        <v>78392</v>
+        <v>98154</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483465</v>
+        <v>483406</v>
       </c>
       <c r="R63" t="n">
-        <v>6948486</v>
+        <v>6948521</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178691</v>
+        <v>122178699</v>
       </c>
       <c r="B64" t="n">
-        <v>98141</v>
+        <v>98237</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7483,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483406</v>
+        <v>483311</v>
       </c>
       <c r="R64" t="n">
-        <v>6948521</v>
+        <v>6948661</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178677</v>
+        <v>122178687</v>
       </c>
       <c r="B65" t="n">
-        <v>97178</v>
+        <v>79737</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7585,25 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483297</v>
+        <v>483437</v>
       </c>
       <c r="R65" t="n">
-        <v>6948492</v>
+        <v>6948523</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178698</v>
+        <v>122178697</v>
       </c>
       <c r="B66" t="n">
-        <v>98224</v>
+        <v>97191</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483316</v>
+        <v>483357</v>
       </c>
       <c r="R66" t="n">
-        <v>6948659</v>
+        <v>6948607</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178676</v>
+        <v>122178701</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483258</v>
+        <v>483306</v>
       </c>
       <c r="R67" t="n">
-        <v>6948497</v>
+        <v>6948674</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178689</v>
+        <v>122178695</v>
       </c>
       <c r="B68" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7895,21 +7895,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483427</v>
+        <v>483360</v>
       </c>
       <c r="R68" t="n">
-        <v>6948511</v>
+        <v>6948597</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178678</v>
+        <v>122178684</v>
       </c>
       <c r="B69" t="n">
-        <v>98128</v>
+        <v>79737</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483411</v>
+        <v>483433</v>
       </c>
       <c r="R69" t="n">
-        <v>6948445</v>
+        <v>6948515</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178693</v>
+        <v>122178680</v>
       </c>
       <c r="B70" t="n">
-        <v>98245</v>
+        <v>79641</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8099,21 +8099,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483400</v>
+        <v>483471</v>
       </c>
       <c r="R70" t="n">
-        <v>6948533</v>
+        <v>6948473</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178699</v>
+        <v>122178682</v>
       </c>
       <c r="B71" t="n">
-        <v>98224</v>
+        <v>98258</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483311</v>
+        <v>483452</v>
       </c>
       <c r="R71" t="n">
-        <v>6948661</v>
+        <v>6948488</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178727</v>
+        <v>122178693</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8299,25 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>482951</v>
+        <v>483400</v>
       </c>
       <c r="R72" t="n">
-        <v>6948660</v>
+        <v>6948533</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178701</v>
+        <v>122178689</v>
       </c>
       <c r="B73" t="n">
         <v>79737</v>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483306</v>
+        <v>483427</v>
       </c>
       <c r="R73" t="n">
-        <v>6948674</v>
+        <v>6948511</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178686</v>
+        <v>122178683</v>
       </c>
       <c r="B74" t="n">
-        <v>98245</v>
+        <v>98237</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483445</v>
+        <v>483448</v>
       </c>
       <c r="R74" t="n">
-        <v>6948521</v>
+        <v>6948496</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178679</v>
+        <v>122178700</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483412</v>
+        <v>483303</v>
       </c>
       <c r="R75" t="n">
-        <v>6948450</v>
+        <v>6948673</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178703</v>
+        <v>122178672</v>
       </c>
       <c r="B42" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483313</v>
+        <v>483111</v>
       </c>
       <c r="R42" t="n">
-        <v>6948690</v>
+        <v>6948568</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178672</v>
+        <v>122178703</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483111</v>
+        <v>483313</v>
       </c>
       <c r="R43" t="n">
-        <v>6948568</v>
+        <v>6948690</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178685</v>
+        <v>122178671</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>78393</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483448</v>
+        <v>483025</v>
       </c>
       <c r="R41" t="n">
-        <v>6948530</v>
+        <v>6948533</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178672</v>
+        <v>122178669</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483111</v>
+        <v>482972</v>
       </c>
       <c r="R42" t="n">
-        <v>6948568</v>
+        <v>6948524</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178703</v>
+        <v>122178677</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483313</v>
+        <v>483297</v>
       </c>
       <c r="R43" t="n">
-        <v>6948690</v>
+        <v>6948492</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178698</v>
+        <v>122178682</v>
       </c>
       <c r="B44" t="n">
-        <v>98237</v>
+        <v>98258</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483316</v>
+        <v>483452</v>
       </c>
       <c r="R44" t="n">
-        <v>6948659</v>
+        <v>6948488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178677</v>
+        <v>122178702</v>
       </c>
       <c r="B45" t="n">
         <v>97191</v>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483297</v>
+        <v>483308</v>
       </c>
       <c r="R45" t="n">
-        <v>6948492</v>
+        <v>6948678</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122178669</v>
+        <v>122178726</v>
       </c>
       <c r="B46" t="n">
-        <v>98258</v>
+        <v>78393</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482972</v>
+        <v>483017</v>
       </c>
       <c r="R46" t="n">
-        <v>6948524</v>
+        <v>6948711</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122178725</v>
+        <v>122178727</v>
       </c>
       <c r="B47" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483174</v>
+        <v>482951</v>
       </c>
       <c r="R47" t="n">
-        <v>6948830</v>
+        <v>6948660</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122178726</v>
+        <v>122178685</v>
       </c>
       <c r="B48" t="n">
-        <v>78393</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483017</v>
+        <v>483448</v>
       </c>
       <c r="R48" t="n">
-        <v>6948711</v>
+        <v>6948530</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122178676</v>
+        <v>122178678</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>98141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483258</v>
+        <v>483411</v>
       </c>
       <c r="R49" t="n">
-        <v>6948497</v>
+        <v>6948445</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122178727</v>
+        <v>122178674</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6055,25 +6055,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>482951</v>
+        <v>483168</v>
       </c>
       <c r="R50" t="n">
-        <v>6948660</v>
+        <v>6948539</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122178694</v>
+        <v>122178693</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483393</v>
+        <v>483400</v>
       </c>
       <c r="R51" t="n">
-        <v>6948545</v>
+        <v>6948533</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122178686</v>
+        <v>122178694</v>
       </c>
       <c r="B52" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6259,25 +6259,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483445</v>
+        <v>483393</v>
       </c>
       <c r="R52" t="n">
-        <v>6948521</v>
+        <v>6948545</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122178688</v>
+        <v>122178680</v>
       </c>
       <c r="B53" t="n">
-        <v>79737</v>
+        <v>79641</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,25 +6361,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483425</v>
+        <v>483471</v>
       </c>
       <c r="R53" t="n">
-        <v>6948524</v>
+        <v>6948473</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122178671</v>
+        <v>122178691</v>
       </c>
       <c r="B54" t="n">
-        <v>78393</v>
+        <v>98154</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483025</v>
+        <v>483406</v>
       </c>
       <c r="R54" t="n">
-        <v>6948533</v>
+        <v>6948521</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122178702</v>
+        <v>122178697</v>
       </c>
       <c r="B55" t="n">
         <v>97191</v>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483308</v>
+        <v>483357</v>
       </c>
       <c r="R55" t="n">
-        <v>6948678</v>
+        <v>6948607</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122178679</v>
+        <v>122178673</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6667,25 +6667,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483412</v>
+        <v>483127</v>
       </c>
       <c r="R56" t="n">
-        <v>6948450</v>
+        <v>6948551</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122178681</v>
+        <v>122178725</v>
       </c>
       <c r="B57" t="n">
-        <v>78392</v>
+        <v>97191</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,25 +6769,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483465</v>
+        <v>483174</v>
       </c>
       <c r="R57" t="n">
-        <v>6948486</v>
+        <v>6948830</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178674</v>
+        <v>122178701</v>
       </c>
       <c r="B58" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,25 +6871,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483168</v>
+        <v>483306</v>
       </c>
       <c r="R58" t="n">
-        <v>6948539</v>
+        <v>6948674</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178678</v>
+        <v>122178689</v>
       </c>
       <c r="B59" t="n">
-        <v>98141</v>
+        <v>79737</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6973,25 +6973,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483411</v>
+        <v>483427</v>
       </c>
       <c r="R59" t="n">
-        <v>6948445</v>
+        <v>6948511</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178675</v>
+        <v>122178687</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7075,25 +7075,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483206</v>
+        <v>483437</v>
       </c>
       <c r="R60" t="n">
-        <v>6948535</v>
+        <v>6948523</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178692</v>
+        <v>122178675</v>
       </c>
       <c r="B61" t="n">
-        <v>97191</v>
+        <v>98237</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483406</v>
+        <v>483206</v>
       </c>
       <c r="R61" t="n">
-        <v>6948521</v>
+        <v>6948535</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178673</v>
+        <v>122178688</v>
       </c>
       <c r="B62" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7279,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483127</v>
+        <v>483425</v>
       </c>
       <c r="R62" t="n">
-        <v>6948551</v>
+        <v>6948524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178691</v>
+        <v>122178700</v>
       </c>
       <c r="B63" t="n">
-        <v>98154</v>
+        <v>98258</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7385,21 +7385,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483406</v>
+        <v>483303</v>
       </c>
       <c r="R63" t="n">
-        <v>6948521</v>
+        <v>6948673</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178699</v>
+        <v>122178692</v>
       </c>
       <c r="B64" t="n">
-        <v>98237</v>
+        <v>97191</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7483,25 +7483,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483311</v>
+        <v>483406</v>
       </c>
       <c r="R64" t="n">
-        <v>6948661</v>
+        <v>6948521</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178687</v>
+        <v>122178686</v>
       </c>
       <c r="B65" t="n">
-        <v>79737</v>
+        <v>98258</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7585,25 +7585,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483437</v>
+        <v>483445</v>
       </c>
       <c r="R65" t="n">
-        <v>6948523</v>
+        <v>6948521</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178697</v>
+        <v>122178698</v>
       </c>
       <c r="B66" t="n">
-        <v>97191</v>
+        <v>98237</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7687,25 +7687,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483357</v>
+        <v>483316</v>
       </c>
       <c r="R66" t="n">
-        <v>6948607</v>
+        <v>6948659</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178701</v>
+        <v>122178676</v>
       </c>
       <c r="B67" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483306</v>
+        <v>483258</v>
       </c>
       <c r="R67" t="n">
-        <v>6948674</v>
+        <v>6948497</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178695</v>
+        <v>122178703</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7895,21 +7895,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483360</v>
+        <v>483313</v>
       </c>
       <c r="R68" t="n">
-        <v>6948597</v>
+        <v>6948690</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178684</v>
+        <v>122178683</v>
       </c>
       <c r="B69" t="n">
-        <v>79737</v>
+        <v>98237</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483433</v>
+        <v>483448</v>
       </c>
       <c r="R69" t="n">
-        <v>6948515</v>
+        <v>6948496</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178680</v>
+        <v>122178699</v>
       </c>
       <c r="B70" t="n">
-        <v>79641</v>
+        <v>98237</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8095,25 +8095,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483471</v>
+        <v>483311</v>
       </c>
       <c r="R70" t="n">
-        <v>6948473</v>
+        <v>6948661</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178682</v>
+        <v>122178679</v>
       </c>
       <c r="B71" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483452</v>
+        <v>483412</v>
       </c>
       <c r="R71" t="n">
-        <v>6948488</v>
+        <v>6948450</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178693</v>
+        <v>122178672</v>
       </c>
       <c r="B72" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8299,25 +8299,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483400</v>
+        <v>483111</v>
       </c>
       <c r="R72" t="n">
-        <v>6948533</v>
+        <v>6948568</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178689</v>
+        <v>122178684</v>
       </c>
       <c r="B73" t="n">
         <v>79737</v>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483427</v>
+        <v>483433</v>
       </c>
       <c r="R73" t="n">
-        <v>6948511</v>
+        <v>6948515</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178683</v>
+        <v>122178695</v>
       </c>
       <c r="B74" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8503,25 +8503,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483448</v>
+        <v>483360</v>
       </c>
       <c r="R74" t="n">
-        <v>6948496</v>
+        <v>6948597</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178700</v>
+        <v>122178681</v>
       </c>
       <c r="B75" t="n">
-        <v>98258</v>
+        <v>78392</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8605,25 +8605,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483303</v>
+        <v>483465</v>
       </c>
       <c r="R75" t="n">
-        <v>6948673</v>
+        <v>6948486</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8693,6 +8693,120 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126183732</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57755</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>483373</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6948564</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Trolig familjegrupp</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -8698,7 +8698,7 @@
         <v>126183732</v>
       </c>
       <c r="B76" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -8698,7 +8698,7 @@
         <v>126183732</v>
       </c>
       <c r="B76" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 16678-2024 artfynd.xlsx
+++ b/artfynd/A 16678-2024 artfynd.xlsx
@@ -8698,7 +8698,7 @@
         <v>126183732</v>
       </c>
       <c r="B76" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
